--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14E5157-4502-4B32-924A-7317CA476A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100EE0C4-FD3B-41D8-B5C5-01A8EAA67346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="78225" yWindow="1410" windowWidth="17280" windowHeight="18765" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58095" yWindow="3090" windowWidth="21585" windowHeight="17475" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -103,13 +103,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F460"/>
+  <dimension ref="A1:F468"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="4" max="4" width="9.23046875" customWidth="1"/>
@@ -9398,243 +9396,403 @@
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A449" s="2">
+      <c r="A449">
         <v>6940</v>
       </c>
-      <c r="B449" s="3">
+      <c r="B449">
         <v>24</v>
       </c>
-      <c r="C449" s="3">
+      <c r="C449">
         <v>53</v>
       </c>
-      <c r="D449" s="3">
+      <c r="D449">
         <v>66</v>
       </c>
-      <c r="E449" s="3">
+      <c r="E449">
         <v>73</v>
       </c>
-      <c r="F449" s="3">
+      <c r="F449">
         <v>77</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A450" s="2">
+      <c r="A450">
         <v>6941</v>
       </c>
-      <c r="B450" s="3">
+      <c r="B450">
         <v>12</v>
       </c>
-      <c r="C450" s="3">
+      <c r="C450">
         <v>32</v>
       </c>
-      <c r="D450" s="3">
+      <c r="D450">
         <v>34</v>
       </c>
-      <c r="E450" s="3">
+      <c r="E450">
         <v>57</v>
       </c>
-      <c r="F450" s="3">
+      <c r="F450">
         <v>64</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A451" s="2">
+      <c r="A451">
         <v>6942</v>
       </c>
-      <c r="B451" s="3">
+      <c r="B451">
         <v>16</v>
       </c>
-      <c r="C451" s="3">
+      <c r="C451">
         <v>33</v>
       </c>
-      <c r="D451" s="3">
+      <c r="D451">
         <v>34</v>
       </c>
-      <c r="E451" s="3">
+      <c r="E451">
         <v>50</v>
       </c>
-      <c r="F451" s="3">
+      <c r="F451">
         <v>71</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A452" s="2">
+      <c r="A452">
         <v>6943</v>
       </c>
-      <c r="B452" s="3">
+      <c r="B452">
         <v>22</v>
       </c>
-      <c r="C452" s="3">
+      <c r="C452">
         <v>23</v>
       </c>
-      <c r="D452" s="3">
+      <c r="D452">
         <v>35</v>
       </c>
-      <c r="E452" s="3">
+      <c r="E452">
         <v>40</v>
       </c>
-      <c r="F452" s="3">
+      <c r="F452">
         <v>44</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A453" s="2">
+      <c r="A453">
         <v>6944</v>
       </c>
-      <c r="B453" s="3">
+      <c r="B453">
         <v>2</v>
       </c>
-      <c r="C453" s="3">
+      <c r="C453">
         <v>8</v>
       </c>
-      <c r="D453" s="3">
+      <c r="D453">
         <v>30</v>
       </c>
-      <c r="E453" s="3">
+      <c r="E453">
         <v>56</v>
       </c>
-      <c r="F453" s="3">
+      <c r="F453">
         <v>61</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A454" s="2">
+      <c r="A454">
         <v>6945</v>
       </c>
-      <c r="B454" s="3">
+      <c r="B454">
         <v>33</v>
       </c>
-      <c r="C454" s="3">
+      <c r="C454">
         <v>61</v>
       </c>
-      <c r="D454" s="3">
+      <c r="D454">
         <v>66</v>
       </c>
-      <c r="E454" s="3">
+      <c r="E454">
         <v>68</v>
       </c>
-      <c r="F454" s="3">
+      <c r="F454">
         <v>70</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A455" s="2">
+      <c r="A455">
         <v>6946</v>
       </c>
-      <c r="B455" s="3">
+      <c r="B455">
         <v>1</v>
       </c>
-      <c r="C455" s="3">
+      <c r="C455">
         <v>48</v>
       </c>
-      <c r="D455" s="3">
+      <c r="D455">
         <v>53</v>
       </c>
-      <c r="E455" s="3">
+      <c r="E455">
         <v>75</v>
       </c>
-      <c r="F455" s="3">
+      <c r="F455">
         <v>80</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A456" s="2">
+      <c r="A456">
         <v>6947</v>
       </c>
-      <c r="B456" s="3">
+      <c r="B456">
         <v>6</v>
       </c>
-      <c r="C456" s="3">
+      <c r="C456">
         <v>30</v>
       </c>
-      <c r="D456" s="3">
+      <c r="D456">
         <v>52</v>
       </c>
-      <c r="E456" s="3">
+      <c r="E456">
         <v>60</v>
       </c>
-      <c r="F456" s="3">
+      <c r="F456">
         <v>79</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A457" s="2">
+      <c r="A457">
         <v>6948</v>
       </c>
-      <c r="B457" s="3">
+      <c r="B457">
         <v>3</v>
       </c>
-      <c r="C457" s="3">
+      <c r="C457">
         <v>21</v>
       </c>
-      <c r="D457" s="3">
+      <c r="D457">
         <v>32</v>
       </c>
-      <c r="E457" s="3">
+      <c r="E457">
         <v>46</v>
       </c>
-      <c r="F457" s="3">
+      <c r="F457">
         <v>57</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A458" s="2">
+      <c r="A458">
         <v>6949</v>
       </c>
-      <c r="B458" s="3">
+      <c r="B458">
         <v>21</v>
       </c>
-      <c r="C458" s="3">
+      <c r="C458">
         <v>51</v>
       </c>
-      <c r="D458" s="3">
+      <c r="D458">
         <v>60</v>
       </c>
-      <c r="E458" s="3">
+      <c r="E458">
         <v>67</v>
       </c>
-      <c r="F458" s="3">
+      <c r="F458">
         <v>73</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A459" s="2">
+      <c r="A459">
         <v>6950</v>
       </c>
-      <c r="B459" s="3">
+      <c r="B459">
         <v>1</v>
       </c>
-      <c r="C459" s="3">
+      <c r="C459">
         <v>6</v>
       </c>
-      <c r="D459" s="3">
+      <c r="D459">
         <v>24</v>
       </c>
-      <c r="E459" s="3">
+      <c r="E459">
         <v>47</v>
       </c>
-      <c r="F459" s="3">
+      <c r="F459">
         <v>60</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A460" s="2">
+      <c r="A460">
         <v>6951</v>
       </c>
-      <c r="B460" s="3">
+      <c r="B460">
         <v>1</v>
       </c>
-      <c r="C460" s="3">
+      <c r="C460">
         <v>10</v>
       </c>
-      <c r="D460" s="3">
+      <c r="D460">
         <v>20</v>
       </c>
-      <c r="E460" s="3">
+      <c r="E460">
         <v>44</v>
       </c>
-      <c r="F460" s="3">
+      <c r="F460">
         <v>66</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A461">
+        <v>6952</v>
+      </c>
+      <c r="B461">
+        <v>1</v>
+      </c>
+      <c r="C461">
+        <v>2</v>
+      </c>
+      <c r="D461">
+        <v>57</v>
+      </c>
+      <c r="E461">
+        <v>62</v>
+      </c>
+      <c r="F461">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A462">
+        <v>6953</v>
+      </c>
+      <c r="B462">
+        <v>7</v>
+      </c>
+      <c r="C462">
+        <v>22</v>
+      </c>
+      <c r="D462">
+        <v>35</v>
+      </c>
+      <c r="E462">
+        <v>58</v>
+      </c>
+      <c r="F462">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A463">
+        <v>6954</v>
+      </c>
+      <c r="B463">
+        <v>2</v>
+      </c>
+      <c r="C463">
+        <v>29</v>
+      </c>
+      <c r="D463">
+        <v>34</v>
+      </c>
+      <c r="E463">
+        <v>44</v>
+      </c>
+      <c r="F463">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A464">
+        <v>6955</v>
+      </c>
+      <c r="B464">
+        <v>6</v>
+      </c>
+      <c r="C464">
+        <v>8</v>
+      </c>
+      <c r="D464">
+        <v>18</v>
+      </c>
+      <c r="E464">
+        <v>23</v>
+      </c>
+      <c r="F464">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A465">
+        <v>6956</v>
+      </c>
+      <c r="B465">
+        <v>10</v>
+      </c>
+      <c r="C465">
+        <v>38</v>
+      </c>
+      <c r="D465">
+        <v>51</v>
+      </c>
+      <c r="E465">
+        <v>64</v>
+      </c>
+      <c r="F465">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A466">
+        <v>6957</v>
+      </c>
+      <c r="B466">
+        <v>11</v>
+      </c>
+      <c r="C466">
+        <v>14</v>
+      </c>
+      <c r="D466">
+        <v>18</v>
+      </c>
+      <c r="E466">
+        <v>67</v>
+      </c>
+      <c r="F466">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A467">
+        <v>6958</v>
+      </c>
+      <c r="B467">
+        <v>9</v>
+      </c>
+      <c r="C467">
+        <v>14</v>
+      </c>
+      <c r="D467">
+        <v>24</v>
+      </c>
+      <c r="E467">
+        <v>55</v>
+      </c>
+      <c r="F467">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A468">
+        <v>6959</v>
+      </c>
+      <c r="B468">
+        <v>7</v>
+      </c>
+      <c r="C468">
+        <v>12</v>
+      </c>
+      <c r="D468">
+        <v>27</v>
+      </c>
+      <c r="E468">
+        <v>49</v>
+      </c>
+      <c r="F468">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -9643,6 +9801,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-07T04:02:34+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -9810,16 +9978,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-07T04:02:34+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -9830,6 +9988,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9849,17 +10018,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100EE0C4-FD3B-41D8-B5C5-01A8EAA67346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD50F606-0AD9-444A-B9ED-AAE479B8F3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58095" yWindow="3090" windowWidth="21585" windowHeight="17475" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="61275" yWindow="3135" windowWidth="19485" windowHeight="18465" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -428,14 +428,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F468"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:F502"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="9.23046875" customWidth="1"/>
+    <col min="4" max="4" width="9.19921875" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -455,7 +455,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>6493</v>
       </c>
@@ -475,7 +475,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>6494</v>
       </c>
@@ -495,7 +495,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>6495</v>
       </c>
@@ -515,7 +515,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>6496</v>
       </c>
@@ -535,7 +535,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>6497</v>
       </c>
@@ -555,7 +555,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6498</v>
       </c>
@@ -575,7 +575,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>6499</v>
       </c>
@@ -595,7 +595,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>6500</v>
       </c>
@@ -615,7 +615,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>6501</v>
       </c>
@@ -635,7 +635,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>6502</v>
       </c>
@@ -655,7 +655,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>6503</v>
       </c>
@@ -675,7 +675,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>6504</v>
       </c>
@@ -695,7 +695,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>6505</v>
       </c>
@@ -715,7 +715,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>6506</v>
       </c>
@@ -735,7 +735,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>6507</v>
       </c>
@@ -755,7 +755,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>6508</v>
       </c>
@@ -775,7 +775,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>6509</v>
       </c>
@@ -795,7 +795,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>6510</v>
       </c>
@@ -815,7 +815,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>6511</v>
       </c>
@@ -835,7 +835,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>6512</v>
       </c>
@@ -855,7 +855,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>6513</v>
       </c>
@@ -875,7 +875,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>6514</v>
       </c>
@@ -895,7 +895,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>6515</v>
       </c>
@@ -915,7 +915,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>6516</v>
       </c>
@@ -935,7 +935,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>6517</v>
       </c>
@@ -955,7 +955,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>6518</v>
       </c>
@@ -975,7 +975,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>6519</v>
       </c>
@@ -995,7 +995,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>6520</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>6521</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>6522</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>6523</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>6524</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>6525</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>6526</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>6527</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>6528</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>6529</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>6530</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>6531</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>6532</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>6533</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>6534</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>6535</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>6536</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>6537</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>6538</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>6539</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>6540</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>6541</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>6542</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>6543</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>6544</v>
       </c>
@@ -1495,7 +1495,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>6545</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>6546</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>6547</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>6548</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>6549</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>6550</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>6551</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>6552</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>6553</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>6554</v>
       </c>
@@ -1695,7 +1695,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>6555</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>6556</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>6557</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>6558</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>6559</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>6560</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>6561</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>6562</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>6563</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>6564</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>6565</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>6566</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>6567</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>6568</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>6569</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>6570</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>6571</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>6572</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>6573</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>6574</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>6575</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>6576</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>6577</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>6578</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>6579</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>6580</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>6581</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>6582</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>6583</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>6584</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>6585</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>6586</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>6587</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>6588</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>6589</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>6590</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>6591</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>6592</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>6593</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>6594</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>6595</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>6596</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>6597</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>6598</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>6599</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>6600</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>6601</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>6602</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>6603</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>6604</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>6605</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>6606</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>6607</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>6608</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>6609</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>6610</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>6611</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>6612</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>6613</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>6614</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>6615</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>6616</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>6617</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>6618</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>6619</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>6620</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>6621</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>6622</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>6623</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>6624</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>6625</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>6626</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>6627</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>6628</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>6629</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>6630</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>6631</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>6632</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>6633</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>6634</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>6635</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>6636</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>6637</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>6638</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>6639</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>6640</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>6641</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>6642</v>
       </c>
@@ -3455,7 +3455,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>6643</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>6644</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>6645</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>6646</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>6647</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>6648</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>6649</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>6650</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>6651</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>6652</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>6653</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>6654</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>6655</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>6656</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>6657</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>6658</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>6659</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>6660</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>6661</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>6662</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>6663</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>6664</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>6665</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>6666</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>6667</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>6668</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>6669</v>
       </c>
@@ -3995,7 +3995,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>6670</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>6671</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>6672</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>6673</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>6674</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>6675</v>
       </c>
@@ -4115,7 +4115,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>6676</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>6677</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>6678</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>6679</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>6680</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>6681</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>6682</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>6683</v>
       </c>
@@ -4275,7 +4275,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>6684</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>6685</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>6686</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>6687</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>6688</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>6689</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>6690</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>6691</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A201">
         <v>6692</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>6693</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>6694</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>6695</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>6696</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>6697</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>6698</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>6699</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>6700</v>
       </c>
@@ -4615,7 +4615,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>6701</v>
       </c>
@@ -4635,7 +4635,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>6702</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>6703</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>6704</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>6705</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>6706</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>6707</v>
       </c>
@@ -4755,7 +4755,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>6708</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>6709</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>6710</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>6711</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>6712</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>6713</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>6714</v>
       </c>
@@ -4895,7 +4895,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>6715</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>6716</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>6717</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>6718</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>6719</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>6720</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>6721</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>6722</v>
       </c>
@@ -5055,7 +5055,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>6723</v>
       </c>
@@ -5075,7 +5075,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>6724</v>
       </c>
@@ -5095,7 +5095,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>6725</v>
       </c>
@@ -5115,7 +5115,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>6726</v>
       </c>
@@ -5135,7 +5135,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>6727</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>6728</v>
       </c>
@@ -5175,7 +5175,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>6729</v>
       </c>
@@ -5195,7 +5195,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>6730</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>6731</v>
       </c>
@@ -5235,7 +5235,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>6732</v>
       </c>
@@ -5255,7 +5255,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>6733</v>
       </c>
@@ -5275,7 +5275,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>6734</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>6735</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>6736</v>
       </c>
@@ -5335,7 +5335,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>6737</v>
       </c>
@@ -5355,7 +5355,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>6738</v>
       </c>
@@ -5375,7 +5375,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>6739</v>
       </c>
@@ -5395,7 +5395,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>6740</v>
       </c>
@@ -5415,7 +5415,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>6741</v>
       </c>
@@ -5435,7 +5435,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>6742</v>
       </c>
@@ -5455,7 +5455,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>6743</v>
       </c>
@@ -5475,7 +5475,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>6744</v>
       </c>
@@ -5495,7 +5495,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>6745</v>
       </c>
@@ -5515,7 +5515,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>6746</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>6747</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>6748</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>6749</v>
       </c>
@@ -5595,7 +5595,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>6750</v>
       </c>
@@ -5615,7 +5615,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>6751</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>6752</v>
       </c>
@@ -5655,7 +5655,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>6753</v>
       </c>
@@ -5675,7 +5675,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>6754</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>6755</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>6756</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>6757</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>6758</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>6759</v>
       </c>
@@ -5795,7 +5795,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>6760</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>6761</v>
       </c>
@@ -5835,7 +5835,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>6762</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>6763</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>6764</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>6765</v>
       </c>
@@ -5915,7 +5915,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>6766</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>6767</v>
       </c>
@@ -5955,7 +5955,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>6768</v>
       </c>
@@ -5975,7 +5975,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>6769</v>
       </c>
@@ -5995,7 +5995,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>6770</v>
       </c>
@@ -6015,7 +6015,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>6771</v>
       </c>
@@ -6035,7 +6035,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>6772</v>
       </c>
@@ -6055,7 +6055,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>6773</v>
       </c>
@@ -6075,7 +6075,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>6774</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>6775</v>
       </c>
@@ -6115,7 +6115,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>6776</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>6777</v>
       </c>
@@ -6155,7 +6155,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>6778</v>
       </c>
@@ -6175,7 +6175,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>6779</v>
       </c>
@@ -6195,7 +6195,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>6780</v>
       </c>
@@ -6215,7 +6215,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>6781</v>
       </c>
@@ -6235,7 +6235,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>6782</v>
       </c>
@@ -6255,7 +6255,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>6783</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>6784</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>6785</v>
       </c>
@@ -6315,7 +6315,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>6786</v>
       </c>
@@ -6335,7 +6335,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>6787</v>
       </c>
@@ -6355,7 +6355,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>6788</v>
       </c>
@@ -6375,7 +6375,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>6789</v>
       </c>
@@ -6395,7 +6395,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>6790</v>
       </c>
@@ -6415,7 +6415,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>6791</v>
       </c>
@@ -6435,7 +6435,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>6792</v>
       </c>
@@ -6455,7 +6455,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>6793</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>6794</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>6795</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>6796</v>
       </c>
@@ -6535,7 +6535,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>6797</v>
       </c>
@@ -6555,7 +6555,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A307">
         <v>6798</v>
       </c>
@@ -6575,7 +6575,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>6799</v>
       </c>
@@ -6595,7 +6595,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>6800</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>6801</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>6802</v>
       </c>
@@ -6655,7 +6655,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>6803</v>
       </c>
@@ -6675,7 +6675,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>6804</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>6805</v>
       </c>
@@ -6715,7 +6715,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A315">
         <v>6806</v>
       </c>
@@ -6735,7 +6735,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>6807</v>
       </c>
@@ -6755,7 +6755,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>6808</v>
       </c>
@@ -6775,7 +6775,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>6809</v>
       </c>
@@ -6795,7 +6795,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>6810</v>
       </c>
@@ -6815,7 +6815,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>6811</v>
       </c>
@@ -6835,7 +6835,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>6812</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>6813</v>
       </c>
@@ -6875,7 +6875,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>6814</v>
       </c>
@@ -6895,7 +6895,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>6815</v>
       </c>
@@ -6915,7 +6915,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A325">
         <v>6816</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>6817</v>
       </c>
@@ -6955,7 +6955,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>6818</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>6819</v>
       </c>
@@ -6995,7 +6995,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>6820</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>6821</v>
       </c>
@@ -7035,7 +7035,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>6822</v>
       </c>
@@ -7055,7 +7055,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A332">
         <v>6823</v>
       </c>
@@ -7075,7 +7075,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A333">
         <v>6824</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A334">
         <v>6825</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A335">
         <v>6826</v>
       </c>
@@ -7135,7 +7135,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>6827</v>
       </c>
@@ -7155,7 +7155,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>6828</v>
       </c>
@@ -7175,7 +7175,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>6829</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>6830</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>6831</v>
       </c>
@@ -7235,7 +7235,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>6832</v>
       </c>
@@ -7255,7 +7255,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A342">
         <v>6833</v>
       </c>
@@ -7275,7 +7275,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>6834</v>
       </c>
@@ -7295,7 +7295,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>6835</v>
       </c>
@@ -7315,7 +7315,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>6836</v>
       </c>
@@ -7335,7 +7335,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A346">
         <v>6837</v>
       </c>
@@ -7355,7 +7355,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A347">
         <v>6838</v>
       </c>
@@ -7375,7 +7375,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A348">
         <v>6839</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A349">
         <v>6840</v>
       </c>
@@ -7415,7 +7415,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A350">
         <v>6841</v>
       </c>
@@ -7435,7 +7435,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A351">
         <v>6842</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A352">
         <v>6843</v>
       </c>
@@ -7475,7 +7475,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A353">
         <v>6844</v>
       </c>
@@ -7495,7 +7495,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A354">
         <v>6845</v>
       </c>
@@ -7515,7 +7515,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A355">
         <v>6846</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A356">
         <v>6847</v>
       </c>
@@ -7555,7 +7555,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A357">
         <v>6848</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A358">
         <v>6849</v>
       </c>
@@ -7595,7 +7595,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A359">
         <v>6850</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A360">
         <v>6851</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A361">
         <v>6852</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A362">
         <v>6853</v>
       </c>
@@ -7675,7 +7675,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A363">
         <v>6854</v>
       </c>
@@ -7695,7 +7695,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A364">
         <v>6855</v>
       </c>
@@ -7715,7 +7715,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A365">
         <v>6856</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A366">
         <v>6857</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A367">
         <v>6858</v>
       </c>
@@ -7775,7 +7775,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A368">
         <v>6859</v>
       </c>
@@ -7795,7 +7795,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A369">
         <v>6860</v>
       </c>
@@ -7815,7 +7815,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A370">
         <v>6861</v>
       </c>
@@ -7835,7 +7835,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A371">
         <v>6862</v>
       </c>
@@ -7855,7 +7855,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A372">
         <v>6863</v>
       </c>
@@ -7875,7 +7875,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A373">
         <v>6864</v>
       </c>
@@ -7895,7 +7895,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A374">
         <v>6865</v>
       </c>
@@ -7915,7 +7915,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A375">
         <v>6866</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A376">
         <v>6867</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A377">
         <v>6868</v>
       </c>
@@ -7975,7 +7975,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A378">
         <v>6869</v>
       </c>
@@ -7995,7 +7995,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A379">
         <v>6870</v>
       </c>
@@ -8015,7 +8015,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A380">
         <v>6871</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A381">
         <v>6872</v>
       </c>
@@ -8055,7 +8055,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A382">
         <v>6873</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A383">
         <v>6874</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A384">
         <v>6875</v>
       </c>
@@ -8115,7 +8115,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A385">
         <v>6876</v>
       </c>
@@ -8135,7 +8135,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A386">
         <v>6877</v>
       </c>
@@ -8155,7 +8155,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A387">
         <v>6878</v>
       </c>
@@ -8175,7 +8175,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A388">
         <v>6879</v>
       </c>
@@ -8195,7 +8195,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A389">
         <v>6880</v>
       </c>
@@ -8215,7 +8215,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A390">
         <v>6881</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A391">
         <v>6882</v>
       </c>
@@ -8255,7 +8255,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>6883</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A393">
         <v>6884</v>
       </c>
@@ -8295,7 +8295,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A394">
         <v>6885</v>
       </c>
@@ -8315,7 +8315,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A395">
         <v>6886</v>
       </c>
@@ -8335,7 +8335,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A396">
         <v>6887</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A397">
         <v>6888</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A398">
         <v>6889</v>
       </c>
@@ -8395,7 +8395,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A399">
         <v>6890</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A400">
         <v>6891</v>
       </c>
@@ -8435,7 +8435,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A401">
         <v>6892</v>
       </c>
@@ -8455,7 +8455,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A402">
         <v>6893</v>
       </c>
@@ -8475,7 +8475,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A403">
         <v>6894</v>
       </c>
@@ -8495,7 +8495,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A404">
         <v>6895</v>
       </c>
@@ -8515,7 +8515,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A405">
         <v>6896</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A406">
         <v>6897</v>
       </c>
@@ -8555,7 +8555,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A407">
         <v>6898</v>
       </c>
@@ -8575,7 +8575,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A408">
         <v>6899</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A409">
         <v>6900</v>
       </c>
@@ -8615,7 +8615,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A410">
         <v>6901</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A411">
         <v>6902</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A412">
         <v>6903</v>
       </c>
@@ -8675,7 +8675,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A413">
         <v>6904</v>
       </c>
@@ -8695,7 +8695,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A414">
         <v>6905</v>
       </c>
@@ -8715,7 +8715,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A415">
         <v>6906</v>
       </c>
@@ -8735,7 +8735,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A416">
         <v>6907</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A417">
         <v>6908</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A418">
         <v>6909</v>
       </c>
@@ -8795,7 +8795,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A419">
         <v>6910</v>
       </c>
@@ -8815,7 +8815,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A420">
         <v>6911</v>
       </c>
@@ -8835,7 +8835,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A421">
         <v>6912</v>
       </c>
@@ -8855,7 +8855,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A422">
         <v>6913</v>
       </c>
@@ -8875,7 +8875,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A423">
         <v>6914</v>
       </c>
@@ -8895,7 +8895,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A424">
         <v>6915</v>
       </c>
@@ -8915,7 +8915,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A425">
         <v>6916</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A426">
         <v>6917</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A427">
         <v>6918</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A428">
         <v>6919</v>
       </c>
@@ -8995,7 +8995,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A429">
         <v>6920</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A430">
         <v>6921</v>
       </c>
@@ -9035,7 +9035,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A431">
         <v>6922</v>
       </c>
@@ -9055,7 +9055,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A432">
         <v>6923</v>
       </c>
@@ -9075,7 +9075,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A433">
         <v>6924</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A434">
         <v>6925</v>
       </c>
@@ -9115,7 +9115,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A435">
         <v>6926</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A436">
         <v>6927</v>
       </c>
@@ -9155,7 +9155,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A437">
         <v>6928</v>
       </c>
@@ -9175,7 +9175,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A438">
         <v>6929</v>
       </c>
@@ -9195,7 +9195,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A439">
         <v>6930</v>
       </c>
@@ -9215,7 +9215,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A440">
         <v>6931</v>
       </c>
@@ -9235,7 +9235,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A441">
         <v>6932</v>
       </c>
@@ -9255,7 +9255,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A442">
         <v>6933</v>
       </c>
@@ -9275,7 +9275,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A443">
         <v>6934</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A444">
         <v>6935</v>
       </c>
@@ -9315,7 +9315,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A445">
         <v>6936</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A446">
         <v>6937</v>
       </c>
@@ -9355,7 +9355,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A447">
         <v>6938</v>
       </c>
@@ -9375,7 +9375,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A448">
         <v>6939</v>
       </c>
@@ -9395,7 +9395,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A449">
         <v>6940</v>
       </c>
@@ -9415,7 +9415,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A450">
         <v>6941</v>
       </c>
@@ -9435,7 +9435,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A451">
         <v>6942</v>
       </c>
@@ -9455,7 +9455,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A452">
         <v>6943</v>
       </c>
@@ -9475,7 +9475,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A453">
         <v>6944</v>
       </c>
@@ -9495,7 +9495,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A454">
         <v>6945</v>
       </c>
@@ -9515,7 +9515,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A455">
         <v>6946</v>
       </c>
@@ -9535,7 +9535,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A456">
         <v>6947</v>
       </c>
@@ -9555,7 +9555,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A457">
         <v>6948</v>
       </c>
@@ -9575,7 +9575,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A458">
         <v>6949</v>
       </c>
@@ -9595,7 +9595,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A459">
         <v>6950</v>
       </c>
@@ -9615,7 +9615,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A460">
         <v>6951</v>
       </c>
@@ -9635,7 +9635,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A461">
         <v>6952</v>
       </c>
@@ -9655,7 +9655,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A462">
         <v>6953</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A463">
         <v>6954</v>
       </c>
@@ -9695,7 +9695,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A464">
         <v>6955</v>
       </c>
@@ -9715,7 +9715,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A465">
         <v>6956</v>
       </c>
@@ -9735,7 +9735,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A466">
         <v>6957</v>
       </c>
@@ -9755,7 +9755,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A467">
         <v>6958</v>
       </c>
@@ -9775,7 +9775,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A468">
         <v>6959</v>
       </c>
@@ -9793,6 +9793,686 @@
       </c>
       <c r="F468">
         <v>54</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A469">
+        <v>6960</v>
+      </c>
+      <c r="B469">
+        <v>7</v>
+      </c>
+      <c r="C469">
+        <v>8</v>
+      </c>
+      <c r="D469">
+        <v>14</v>
+      </c>
+      <c r="E469">
+        <v>39</v>
+      </c>
+      <c r="F469">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A470">
+        <v>6961</v>
+      </c>
+      <c r="B470">
+        <v>15</v>
+      </c>
+      <c r="C470">
+        <v>45</v>
+      </c>
+      <c r="D470">
+        <v>55</v>
+      </c>
+      <c r="E470">
+        <v>62</v>
+      </c>
+      <c r="F470">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A471">
+        <v>6962</v>
+      </c>
+      <c r="B471">
+        <v>15</v>
+      </c>
+      <c r="C471">
+        <v>25</v>
+      </c>
+      <c r="D471">
+        <v>37</v>
+      </c>
+      <c r="E471">
+        <v>79</v>
+      </c>
+      <c r="F471">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="472" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A472">
+        <v>6963</v>
+      </c>
+      <c r="B472">
+        <v>6</v>
+      </c>
+      <c r="C472">
+        <v>19</v>
+      </c>
+      <c r="D472">
+        <v>29</v>
+      </c>
+      <c r="E472">
+        <v>62</v>
+      </c>
+      <c r="F472">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A473">
+        <v>6964</v>
+      </c>
+      <c r="B473">
+        <v>3</v>
+      </c>
+      <c r="C473">
+        <v>9</v>
+      </c>
+      <c r="D473">
+        <v>30</v>
+      </c>
+      <c r="E473">
+        <v>56</v>
+      </c>
+      <c r="F473">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A474">
+        <v>6965</v>
+      </c>
+      <c r="B474">
+        <v>7</v>
+      </c>
+      <c r="C474">
+        <v>12</v>
+      </c>
+      <c r="D474">
+        <v>26</v>
+      </c>
+      <c r="E474">
+        <v>68</v>
+      </c>
+      <c r="F474">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A475">
+        <v>6966</v>
+      </c>
+      <c r="B475">
+        <v>9</v>
+      </c>
+      <c r="C475">
+        <v>19</v>
+      </c>
+      <c r="D475">
+        <v>26</v>
+      </c>
+      <c r="E475">
+        <v>28</v>
+      </c>
+      <c r="F475">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A476">
+        <v>6967</v>
+      </c>
+      <c r="B476">
+        <v>26</v>
+      </c>
+      <c r="C476">
+        <v>47</v>
+      </c>
+      <c r="D476">
+        <v>68</v>
+      </c>
+      <c r="E476">
+        <v>74</v>
+      </c>
+      <c r="F476">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A477">
+        <v>6968</v>
+      </c>
+      <c r="B477">
+        <v>8</v>
+      </c>
+      <c r="C477">
+        <v>14</v>
+      </c>
+      <c r="D477">
+        <v>44</v>
+      </c>
+      <c r="E477">
+        <v>56</v>
+      </c>
+      <c r="F477">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A478">
+        <v>6969</v>
+      </c>
+      <c r="B478">
+        <v>24</v>
+      </c>
+      <c r="C478">
+        <v>35</v>
+      </c>
+      <c r="D478">
+        <v>37</v>
+      </c>
+      <c r="E478">
+        <v>39</v>
+      </c>
+      <c r="F478">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A479">
+        <v>6970</v>
+      </c>
+      <c r="B479">
+        <v>31</v>
+      </c>
+      <c r="C479">
+        <v>41</v>
+      </c>
+      <c r="D479">
+        <v>47</v>
+      </c>
+      <c r="E479">
+        <v>59</v>
+      </c>
+      <c r="F479">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A480">
+        <v>6971</v>
+      </c>
+      <c r="B480">
+        <v>27</v>
+      </c>
+      <c r="C480">
+        <v>56</v>
+      </c>
+      <c r="D480">
+        <v>64</v>
+      </c>
+      <c r="E480">
+        <v>65</v>
+      </c>
+      <c r="F480">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="481" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A481">
+        <v>6972</v>
+      </c>
+      <c r="B481">
+        <v>12</v>
+      </c>
+      <c r="C481">
+        <v>13</v>
+      </c>
+      <c r="D481">
+        <v>25</v>
+      </c>
+      <c r="E481">
+        <v>33</v>
+      </c>
+      <c r="F481">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="482" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A482">
+        <v>6973</v>
+      </c>
+      <c r="B482">
+        <v>2</v>
+      </c>
+      <c r="C482">
+        <v>11</v>
+      </c>
+      <c r="D482">
+        <v>41</v>
+      </c>
+      <c r="E482">
+        <v>67</v>
+      </c>
+      <c r="F482">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A483">
+        <v>6974</v>
+      </c>
+      <c r="B483">
+        <v>17</v>
+      </c>
+      <c r="C483">
+        <v>27</v>
+      </c>
+      <c r="D483">
+        <v>30</v>
+      </c>
+      <c r="E483">
+        <v>60</v>
+      </c>
+      <c r="F483">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="484" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A484">
+        <v>6975</v>
+      </c>
+      <c r="B484">
+        <v>1</v>
+      </c>
+      <c r="C484">
+        <v>7</v>
+      </c>
+      <c r="D484">
+        <v>13</v>
+      </c>
+      <c r="E484">
+        <v>31</v>
+      </c>
+      <c r="F484">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="485" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A485">
+        <v>6976</v>
+      </c>
+      <c r="B485">
+        <v>4</v>
+      </c>
+      <c r="C485">
+        <v>24</v>
+      </c>
+      <c r="D485">
+        <v>25</v>
+      </c>
+      <c r="E485">
+        <v>62</v>
+      </c>
+      <c r="F485">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A486">
+        <v>6977</v>
+      </c>
+      <c r="B486">
+        <v>6</v>
+      </c>
+      <c r="C486">
+        <v>18</v>
+      </c>
+      <c r="D486">
+        <v>43</v>
+      </c>
+      <c r="E486">
+        <v>56</v>
+      </c>
+      <c r="F486">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A487">
+        <v>6978</v>
+      </c>
+      <c r="B487">
+        <v>9</v>
+      </c>
+      <c r="C487">
+        <v>10</v>
+      </c>
+      <c r="D487">
+        <v>26</v>
+      </c>
+      <c r="E487">
+        <v>44</v>
+      </c>
+      <c r="F487">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A488">
+        <v>6979</v>
+      </c>
+      <c r="B488">
+        <v>20</v>
+      </c>
+      <c r="C488">
+        <v>23</v>
+      </c>
+      <c r="D488">
+        <v>27</v>
+      </c>
+      <c r="E488">
+        <v>32</v>
+      </c>
+      <c r="F488">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A489">
+        <v>6980</v>
+      </c>
+      <c r="B489">
+        <v>7</v>
+      </c>
+      <c r="C489">
+        <v>8</v>
+      </c>
+      <c r="D489">
+        <v>66</v>
+      </c>
+      <c r="E489">
+        <v>76</v>
+      </c>
+      <c r="F489">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A490">
+        <v>6981</v>
+      </c>
+      <c r="B490">
+        <v>7</v>
+      </c>
+      <c r="C490">
+        <v>29</v>
+      </c>
+      <c r="D490">
+        <v>39</v>
+      </c>
+      <c r="E490">
+        <v>59</v>
+      </c>
+      <c r="F490">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A491">
+        <v>6982</v>
+      </c>
+      <c r="B491">
+        <v>21</v>
+      </c>
+      <c r="C491">
+        <v>25</v>
+      </c>
+      <c r="D491">
+        <v>26</v>
+      </c>
+      <c r="E491">
+        <v>42</v>
+      </c>
+      <c r="F491">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A492">
+        <v>6983</v>
+      </c>
+      <c r="B492">
+        <v>24</v>
+      </c>
+      <c r="C492">
+        <v>38</v>
+      </c>
+      <c r="D492">
+        <v>46</v>
+      </c>
+      <c r="E492">
+        <v>77</v>
+      </c>
+      <c r="F492">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="493" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A493">
+        <v>6984</v>
+      </c>
+      <c r="B493">
+        <v>4</v>
+      </c>
+      <c r="C493">
+        <v>15</v>
+      </c>
+      <c r="D493">
+        <v>19</v>
+      </c>
+      <c r="E493">
+        <v>21</v>
+      </c>
+      <c r="F493">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="494" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A494">
+        <v>6985</v>
+      </c>
+      <c r="B494">
+        <v>4</v>
+      </c>
+      <c r="C494">
+        <v>9</v>
+      </c>
+      <c r="D494">
+        <v>39</v>
+      </c>
+      <c r="E494">
+        <v>43</v>
+      </c>
+      <c r="F494">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="495" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A495">
+        <v>6986</v>
+      </c>
+      <c r="B495">
+        <v>18</v>
+      </c>
+      <c r="C495">
+        <v>26</v>
+      </c>
+      <c r="D495">
+        <v>44</v>
+      </c>
+      <c r="E495">
+        <v>51</v>
+      </c>
+      <c r="F495">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="496" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A496">
+        <v>6987</v>
+      </c>
+      <c r="B496">
+        <v>31</v>
+      </c>
+      <c r="C496">
+        <v>36</v>
+      </c>
+      <c r="D496">
+        <v>37</v>
+      </c>
+      <c r="E496">
+        <v>58</v>
+      </c>
+      <c r="F496">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A497">
+        <v>6988</v>
+      </c>
+      <c r="B497">
+        <v>3</v>
+      </c>
+      <c r="C497">
+        <v>9</v>
+      </c>
+      <c r="D497">
+        <v>12</v>
+      </c>
+      <c r="E497">
+        <v>24</v>
+      </c>
+      <c r="F497">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A498">
+        <v>6989</v>
+      </c>
+      <c r="B498">
+        <v>1</v>
+      </c>
+      <c r="C498">
+        <v>17</v>
+      </c>
+      <c r="D498">
+        <v>26</v>
+      </c>
+      <c r="E498">
+        <v>48</v>
+      </c>
+      <c r="F498">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A499">
+        <v>6990</v>
+      </c>
+      <c r="B499">
+        <v>44</v>
+      </c>
+      <c r="C499">
+        <v>59</v>
+      </c>
+      <c r="D499">
+        <v>67</v>
+      </c>
+      <c r="E499">
+        <v>71</v>
+      </c>
+      <c r="F499">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A500">
+        <v>6991</v>
+      </c>
+      <c r="B500">
+        <v>19</v>
+      </c>
+      <c r="C500">
+        <v>21</v>
+      </c>
+      <c r="D500">
+        <v>33</v>
+      </c>
+      <c r="E500">
+        <v>76</v>
+      </c>
+      <c r="F500">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A501">
+        <v>6992</v>
+      </c>
+      <c r="B501">
+        <v>19</v>
+      </c>
+      <c r="C501">
+        <v>46</v>
+      </c>
+      <c r="D501">
+        <v>69</v>
+      </c>
+      <c r="E501">
+        <v>70</v>
+      </c>
+      <c r="F501">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A502">
+        <v>6993</v>
+      </c>
+      <c r="B502">
+        <v>7</v>
+      </c>
+      <c r="C502">
+        <v>17</v>
+      </c>
+      <c r="D502">
+        <v>25</v>
+      </c>
+      <c r="E502">
+        <v>49</v>
+      </c>
+      <c r="F502">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -9801,13 +10481,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-07T04:02:34+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9979,21 +10658,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-07T04:02:34+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10019,9 +10696,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD50F606-0AD9-444A-B9ED-AAE479B8F3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F583754-7334-4734-89E1-FB8ACD45102D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61275" yWindow="3135" windowWidth="19485" windowHeight="18465" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57630" yWindow="330" windowWidth="18675" windowHeight="12840" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F502"/>
+  <dimension ref="A1:F517"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -10475,21 +10475,312 @@
         <v>74</v>
       </c>
     </row>
+    <row r="503" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A503">
+        <v>6994</v>
+      </c>
+      <c r="B503">
+        <v>21</v>
+      </c>
+      <c r="C503">
+        <v>29</v>
+      </c>
+      <c r="D503">
+        <v>44</v>
+      </c>
+      <c r="E503">
+        <v>53</v>
+      </c>
+      <c r="F503">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A504">
+        <v>6995</v>
+      </c>
+      <c r="B504">
+        <v>2</v>
+      </c>
+      <c r="C504">
+        <v>22</v>
+      </c>
+      <c r="D504">
+        <v>44</v>
+      </c>
+      <c r="E504">
+        <v>68</v>
+      </c>
+      <c r="F504">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A505">
+        <v>6996</v>
+      </c>
+      <c r="B505">
+        <v>29</v>
+      </c>
+      <c r="C505">
+        <v>41</v>
+      </c>
+      <c r="D505">
+        <v>53</v>
+      </c>
+      <c r="E505">
+        <v>64</v>
+      </c>
+      <c r="F505">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A506">
+        <v>6997</v>
+      </c>
+      <c r="B506">
+        <v>22</v>
+      </c>
+      <c r="C506">
+        <v>25</v>
+      </c>
+      <c r="D506">
+        <v>26</v>
+      </c>
+      <c r="E506">
+        <v>55</v>
+      </c>
+      <c r="F506">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A507">
+        <v>6998</v>
+      </c>
+      <c r="B507">
+        <v>9</v>
+      </c>
+      <c r="C507">
+        <v>35</v>
+      </c>
+      <c r="D507">
+        <v>45</v>
+      </c>
+      <c r="E507">
+        <v>48</v>
+      </c>
+      <c r="F507">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A508">
+        <v>6999</v>
+      </c>
+      <c r="B508">
+        <v>2</v>
+      </c>
+      <c r="C508">
+        <v>3</v>
+      </c>
+      <c r="D508">
+        <v>24</v>
+      </c>
+      <c r="E508">
+        <v>29</v>
+      </c>
+      <c r="F508">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A509">
+        <v>7000</v>
+      </c>
+      <c r="B509">
+        <v>20</v>
+      </c>
+      <c r="C509">
+        <v>30</v>
+      </c>
+      <c r="D509">
+        <v>53</v>
+      </c>
+      <c r="E509">
+        <v>56</v>
+      </c>
+      <c r="F509">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A510">
+        <v>7001</v>
+      </c>
+      <c r="B510">
+        <v>25</v>
+      </c>
+      <c r="C510">
+        <v>39</v>
+      </c>
+      <c r="D510">
+        <v>49</v>
+      </c>
+      <c r="E510">
+        <v>50</v>
+      </c>
+      <c r="F510">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A511">
+        <v>7002</v>
+      </c>
+      <c r="B511">
+        <v>4</v>
+      </c>
+      <c r="C511">
+        <v>15</v>
+      </c>
+      <c r="D511">
+        <v>34</v>
+      </c>
+      <c r="E511">
+        <v>49</v>
+      </c>
+      <c r="F511">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A512">
+        <v>7003</v>
+      </c>
+      <c r="B512">
+        <v>4</v>
+      </c>
+      <c r="C512">
+        <v>14</v>
+      </c>
+      <c r="D512">
+        <v>18</v>
+      </c>
+      <c r="E512">
+        <v>54</v>
+      </c>
+      <c r="F512">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="513" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A513">
+        <v>7004</v>
+      </c>
+      <c r="B513">
+        <v>23</v>
+      </c>
+      <c r="C513">
+        <v>35</v>
+      </c>
+      <c r="D513">
+        <v>52</v>
+      </c>
+      <c r="E513">
+        <v>56</v>
+      </c>
+      <c r="F513">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="514" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A514">
+        <v>7005</v>
+      </c>
+      <c r="B514">
+        <v>14</v>
+      </c>
+      <c r="C514">
+        <v>17</v>
+      </c>
+      <c r="D514">
+        <v>32</v>
+      </c>
+      <c r="E514">
+        <v>44</v>
+      </c>
+      <c r="F514">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="515" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A515">
+        <v>7006</v>
+      </c>
+      <c r="B515">
+        <v>33</v>
+      </c>
+      <c r="C515">
+        <v>41</v>
+      </c>
+      <c r="D515">
+        <v>48</v>
+      </c>
+      <c r="E515">
+        <v>55</v>
+      </c>
+      <c r="F515">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="516" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A516">
+        <v>7007</v>
+      </c>
+      <c r="B516">
+        <v>8</v>
+      </c>
+      <c r="C516">
+        <v>22</v>
+      </c>
+      <c r="D516">
+        <v>29</v>
+      </c>
+      <c r="E516">
+        <v>63</v>
+      </c>
+      <c r="F516">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="517" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A517">
+        <v>7008</v>
+      </c>
+      <c r="B517">
+        <v>14</v>
+      </c>
+      <c r="C517">
+        <v>23</v>
+      </c>
+      <c r="D517">
+        <v>47</v>
+      </c>
+      <c r="E517">
+        <v>55</v>
+      </c>
+      <c r="F517">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -10657,6 +10948,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -10668,14 +10968,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10695,6 +10987,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F583754-7334-4734-89E1-FB8ACD45102D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E6AEC5-6C16-4AF3-A048-3767EFD60750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57630" yWindow="330" windowWidth="18675" windowHeight="12840" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="66855" yWindow="810" windowWidth="18675" windowHeight="12840" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F517"/>
+  <dimension ref="A1:F519"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -10775,12 +10775,61 @@
         <v>78</v>
       </c>
     </row>
+    <row r="518" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A518">
+        <v>7009</v>
+      </c>
+      <c r="B518">
+        <v>3</v>
+      </c>
+      <c r="C518">
+        <v>20</v>
+      </c>
+      <c r="D518">
+        <v>23</v>
+      </c>
+      <c r="E518">
+        <v>26</v>
+      </c>
+      <c r="F518">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="519" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A519">
+        <v>7010</v>
+      </c>
+      <c r="B519">
+        <v>5</v>
+      </c>
+      <c r="C519">
+        <v>31</v>
+      </c>
+      <c r="D519">
+        <v>32</v>
+      </c>
+      <c r="E519">
+        <v>35</v>
+      </c>
+      <c r="F519">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -10948,15 +10997,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -10968,6 +11008,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10987,14 +11035,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E6AEC5-6C16-4AF3-A048-3767EFD60750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF681A5-5157-4E8E-AD96-25B846D5A372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="66855" yWindow="810" windowWidth="18675" windowHeight="12840" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58395" yWindow="240" windowWidth="18885" windowHeight="12900" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F519"/>
+  <dimension ref="A1:F528"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -10815,21 +10815,192 @@
         <v>47</v>
       </c>
     </row>
+    <row r="520" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A520">
+        <v>7011</v>
+      </c>
+      <c r="B520">
+        <v>9</v>
+      </c>
+      <c r="C520">
+        <v>24</v>
+      </c>
+      <c r="D520">
+        <v>31</v>
+      </c>
+      <c r="E520">
+        <v>45</v>
+      </c>
+      <c r="F520">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="521" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A521">
+        <v>7012</v>
+      </c>
+      <c r="B521">
+        <v>44</v>
+      </c>
+      <c r="C521">
+        <v>53</v>
+      </c>
+      <c r="D521">
+        <v>54</v>
+      </c>
+      <c r="E521">
+        <v>57</v>
+      </c>
+      <c r="F521">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="522" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A522">
+        <v>7013</v>
+      </c>
+      <c r="B522">
+        <v>12</v>
+      </c>
+      <c r="C522">
+        <v>36</v>
+      </c>
+      <c r="D522">
+        <v>37</v>
+      </c>
+      <c r="E522">
+        <v>53</v>
+      </c>
+      <c r="F522">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="523" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A523">
+        <v>7014</v>
+      </c>
+      <c r="B523">
+        <v>11</v>
+      </c>
+      <c r="C523">
+        <v>16</v>
+      </c>
+      <c r="D523">
+        <v>23</v>
+      </c>
+      <c r="E523">
+        <v>42</v>
+      </c>
+      <c r="F523">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="524" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A524">
+        <v>7015</v>
+      </c>
+      <c r="B524">
+        <v>4</v>
+      </c>
+      <c r="C524">
+        <v>13</v>
+      </c>
+      <c r="D524">
+        <v>52</v>
+      </c>
+      <c r="E524">
+        <v>53</v>
+      </c>
+      <c r="F524">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A525">
+        <v>7016</v>
+      </c>
+      <c r="B525">
+        <v>2</v>
+      </c>
+      <c r="C525">
+        <v>29</v>
+      </c>
+      <c r="D525">
+        <v>31</v>
+      </c>
+      <c r="E525">
+        <v>39</v>
+      </c>
+      <c r="F525">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A526">
+        <v>7017</v>
+      </c>
+      <c r="B526">
+        <v>12</v>
+      </c>
+      <c r="C526">
+        <v>35</v>
+      </c>
+      <c r="D526">
+        <v>48</v>
+      </c>
+      <c r="E526">
+        <v>58</v>
+      </c>
+      <c r="F526">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="527" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A527">
+        <v>7018</v>
+      </c>
+      <c r="B527">
+        <v>10</v>
+      </c>
+      <c r="C527">
+        <v>15</v>
+      </c>
+      <c r="D527">
+        <v>17</v>
+      </c>
+      <c r="E527">
+        <v>53</v>
+      </c>
+      <c r="F527">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A528">
+        <v>7019</v>
+      </c>
+      <c r="B528">
+        <v>6</v>
+      </c>
+      <c r="C528">
+        <v>11</v>
+      </c>
+      <c r="D528">
+        <v>42</v>
+      </c>
+      <c r="E528">
+        <v>62</v>
+      </c>
+      <c r="F528">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -10997,6 +11168,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11008,14 +11188,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11035,6 +11207,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF681A5-5157-4E8E-AD96-25B846D5A372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C652A03E-FB68-4C22-A12C-950BC05D736F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58395" yWindow="240" windowWidth="18885" windowHeight="12900" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57690" yWindow="210" windowWidth="15015" windowHeight="14355" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F528"/>
+  <dimension ref="A1:F559"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -10995,12 +10995,641 @@
         <v>78</v>
       </c>
     </row>
+    <row r="529" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A529">
+        <v>7020</v>
+      </c>
+      <c r="B529">
+        <v>23</v>
+      </c>
+      <c r="C529">
+        <v>31</v>
+      </c>
+      <c r="D529">
+        <v>40</v>
+      </c>
+      <c r="E529">
+        <v>41</v>
+      </c>
+      <c r="F529">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="530" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A530">
+        <v>7021</v>
+      </c>
+      <c r="B530">
+        <v>1</v>
+      </c>
+      <c r="C530">
+        <v>24</v>
+      </c>
+      <c r="D530">
+        <v>29</v>
+      </c>
+      <c r="E530">
+        <v>57</v>
+      </c>
+      <c r="F530">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="531" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A531">
+        <v>7022</v>
+      </c>
+      <c r="B531">
+        <v>30</v>
+      </c>
+      <c r="C531">
+        <v>38</v>
+      </c>
+      <c r="D531">
+        <v>47</v>
+      </c>
+      <c r="E531">
+        <v>50</v>
+      </c>
+      <c r="F531">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="532" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A532">
+        <v>7023</v>
+      </c>
+      <c r="B532">
+        <v>16</v>
+      </c>
+      <c r="C532">
+        <v>35</v>
+      </c>
+      <c r="D532">
+        <v>44</v>
+      </c>
+      <c r="E532">
+        <v>66</v>
+      </c>
+      <c r="F532">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="533" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A533">
+        <v>7024</v>
+      </c>
+      <c r="B533">
+        <v>2</v>
+      </c>
+      <c r="C533">
+        <v>38</v>
+      </c>
+      <c r="D533">
+        <v>43</v>
+      </c>
+      <c r="E533">
+        <v>48</v>
+      </c>
+      <c r="F533">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="534" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A534">
+        <v>7025</v>
+      </c>
+      <c r="B534">
+        <v>14</v>
+      </c>
+      <c r="C534">
+        <v>27</v>
+      </c>
+      <c r="D534">
+        <v>29</v>
+      </c>
+      <c r="E534">
+        <v>50</v>
+      </c>
+      <c r="F534">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="535" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A535">
+        <v>7026</v>
+      </c>
+      <c r="B535">
+        <v>19</v>
+      </c>
+      <c r="C535">
+        <v>51</v>
+      </c>
+      <c r="D535">
+        <v>55</v>
+      </c>
+      <c r="E535">
+        <v>57</v>
+      </c>
+      <c r="F535">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="536" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A536">
+        <v>7027</v>
+      </c>
+      <c r="B536">
+        <v>24</v>
+      </c>
+      <c r="C536">
+        <v>27</v>
+      </c>
+      <c r="D536">
+        <v>34</v>
+      </c>
+      <c r="E536">
+        <v>44</v>
+      </c>
+      <c r="F536">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="537" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A537">
+        <v>7028</v>
+      </c>
+      <c r="B537">
+        <v>1</v>
+      </c>
+      <c r="C537">
+        <v>16</v>
+      </c>
+      <c r="D537">
+        <v>41</v>
+      </c>
+      <c r="E537">
+        <v>42</v>
+      </c>
+      <c r="F537">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="538" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A538">
+        <v>7029</v>
+      </c>
+      <c r="B538">
+        <v>13</v>
+      </c>
+      <c r="C538">
+        <v>14</v>
+      </c>
+      <c r="D538">
+        <v>17</v>
+      </c>
+      <c r="E538">
+        <v>20</v>
+      </c>
+      <c r="F538">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="539" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A539">
+        <v>7030</v>
+      </c>
+      <c r="B539">
+        <v>16</v>
+      </c>
+      <c r="C539">
+        <v>19</v>
+      </c>
+      <c r="D539">
+        <v>24</v>
+      </c>
+      <c r="E539">
+        <v>50</v>
+      </c>
+      <c r="F539">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="540" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A540">
+        <v>7031</v>
+      </c>
+      <c r="B540">
+        <v>3</v>
+      </c>
+      <c r="C540">
+        <v>12</v>
+      </c>
+      <c r="D540">
+        <v>40</v>
+      </c>
+      <c r="E540">
+        <v>56</v>
+      </c>
+      <c r="F540">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="541" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A541">
+        <v>7032</v>
+      </c>
+      <c r="B541">
+        <v>5</v>
+      </c>
+      <c r="C541">
+        <v>28</v>
+      </c>
+      <c r="D541">
+        <v>48</v>
+      </c>
+      <c r="E541">
+        <v>49</v>
+      </c>
+      <c r="F541">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="542" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A542">
+        <v>7033</v>
+      </c>
+      <c r="B542">
+        <v>1</v>
+      </c>
+      <c r="C542">
+        <v>29</v>
+      </c>
+      <c r="D542">
+        <v>32</v>
+      </c>
+      <c r="E542">
+        <v>33</v>
+      </c>
+      <c r="F542">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="543" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A543">
+        <v>7034</v>
+      </c>
+      <c r="B543">
+        <v>12</v>
+      </c>
+      <c r="C543">
+        <v>21</v>
+      </c>
+      <c r="D543">
+        <v>74</v>
+      </c>
+      <c r="E543">
+        <v>77</v>
+      </c>
+      <c r="F543">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="544" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A544">
+        <v>7035</v>
+      </c>
+      <c r="B544">
+        <v>14</v>
+      </c>
+      <c r="C544">
+        <v>15</v>
+      </c>
+      <c r="D544">
+        <v>48</v>
+      </c>
+      <c r="E544">
+        <v>58</v>
+      </c>
+      <c r="F544">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A545">
+        <v>7036</v>
+      </c>
+      <c r="B545">
+        <v>15</v>
+      </c>
+      <c r="C545">
+        <v>42</v>
+      </c>
+      <c r="D545">
+        <v>63</v>
+      </c>
+      <c r="E545">
+        <v>66</v>
+      </c>
+      <c r="F545">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="546" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A546">
+        <v>7037</v>
+      </c>
+      <c r="B546">
+        <v>9</v>
+      </c>
+      <c r="C546">
+        <v>26</v>
+      </c>
+      <c r="D546">
+        <v>42</v>
+      </c>
+      <c r="E546">
+        <v>55</v>
+      </c>
+      <c r="F546">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="547" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A547">
+        <v>7038</v>
+      </c>
+      <c r="B547">
+        <v>2</v>
+      </c>
+      <c r="C547">
+        <v>31</v>
+      </c>
+      <c r="D547">
+        <v>39</v>
+      </c>
+      <c r="E547">
+        <v>64</v>
+      </c>
+      <c r="F547">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="548" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A548">
+        <v>7039</v>
+      </c>
+      <c r="B548">
+        <v>12</v>
+      </c>
+      <c r="C548">
+        <v>15</v>
+      </c>
+      <c r="D548">
+        <v>16</v>
+      </c>
+      <c r="E548">
+        <v>67</v>
+      </c>
+      <c r="F548">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A549">
+        <v>7040</v>
+      </c>
+      <c r="B549">
+        <v>5</v>
+      </c>
+      <c r="C549">
+        <v>23</v>
+      </c>
+      <c r="D549">
+        <v>52</v>
+      </c>
+      <c r="E549">
+        <v>56</v>
+      </c>
+      <c r="F549">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="550" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A550">
+        <v>7041</v>
+      </c>
+      <c r="B550">
+        <v>25</v>
+      </c>
+      <c r="C550">
+        <v>28</v>
+      </c>
+      <c r="D550">
+        <v>49</v>
+      </c>
+      <c r="E550">
+        <v>56</v>
+      </c>
+      <c r="F550">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="551" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A551">
+        <v>7042</v>
+      </c>
+      <c r="B551">
+        <v>10</v>
+      </c>
+      <c r="C551">
+        <v>13</v>
+      </c>
+      <c r="D551">
+        <v>25</v>
+      </c>
+      <c r="E551">
+        <v>36</v>
+      </c>
+      <c r="F551">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="552" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A552">
+        <v>7043</v>
+      </c>
+      <c r="B552">
+        <v>10</v>
+      </c>
+      <c r="C552">
+        <v>20</v>
+      </c>
+      <c r="D552">
+        <v>21</v>
+      </c>
+      <c r="E552">
+        <v>29</v>
+      </c>
+      <c r="F552">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="553" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A553">
+        <v>7044</v>
+      </c>
+      <c r="B553">
+        <v>2</v>
+      </c>
+      <c r="C553">
+        <v>5</v>
+      </c>
+      <c r="D553">
+        <v>30</v>
+      </c>
+      <c r="E553">
+        <v>54</v>
+      </c>
+      <c r="F553">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="554" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A554">
+        <v>7045</v>
+      </c>
+      <c r="B554">
+        <v>12</v>
+      </c>
+      <c r="C554">
+        <v>13</v>
+      </c>
+      <c r="D554">
+        <v>17</v>
+      </c>
+      <c r="E554">
+        <v>54</v>
+      </c>
+      <c r="F554">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A555">
+        <v>7046</v>
+      </c>
+      <c r="B555">
+        <v>2</v>
+      </c>
+      <c r="C555">
+        <v>12</v>
+      </c>
+      <c r="D555">
+        <v>37</v>
+      </c>
+      <c r="E555">
+        <v>68</v>
+      </c>
+      <c r="F555">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="556" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A556">
+        <v>7047</v>
+      </c>
+      <c r="B556">
+        <v>6</v>
+      </c>
+      <c r="C556">
+        <v>11</v>
+      </c>
+      <c r="D556">
+        <v>26</v>
+      </c>
+      <c r="E556">
+        <v>50</v>
+      </c>
+      <c r="F556">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A557">
+        <v>7048</v>
+      </c>
+      <c r="B557">
+        <v>9</v>
+      </c>
+      <c r="C557">
+        <v>25</v>
+      </c>
+      <c r="D557">
+        <v>34</v>
+      </c>
+      <c r="E557">
+        <v>56</v>
+      </c>
+      <c r="F557">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="558" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A558">
+        <v>7049</v>
+      </c>
+      <c r="B558">
+        <v>9</v>
+      </c>
+      <c r="C558">
+        <v>14</v>
+      </c>
+      <c r="D558">
+        <v>25</v>
+      </c>
+      <c r="E558">
+        <v>44</v>
+      </c>
+      <c r="F558">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A559">
+        <v>7050</v>
+      </c>
+      <c r="B559">
+        <v>24</v>
+      </c>
+      <c r="C559">
+        <v>36</v>
+      </c>
+      <c r="D559">
+        <v>61</v>
+      </c>
+      <c r="E559">
+        <v>66</v>
+      </c>
+      <c r="F559">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11168,15 +11797,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11188,6 +11808,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11207,14 +11835,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C652A03E-FB68-4C22-A12C-950BC05D736F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFA79B4-22AF-4CAE-ACED-91AB0E9DD58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57690" yWindow="210" windowWidth="15015" windowHeight="14355" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57660" yWindow="75" windowWidth="14910" windowHeight="14565" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -103,11 +103,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F559"/>
+  <dimension ref="A1:F561"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -11615,21 +11617,52 @@
         <v>74</v>
       </c>
     </row>
+    <row r="560" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A560" s="2">
+        <v>7051</v>
+      </c>
+      <c r="B560" s="3">
+        <v>19</v>
+      </c>
+      <c r="C560" s="3">
+        <v>32</v>
+      </c>
+      <c r="D560" s="3">
+        <v>50</v>
+      </c>
+      <c r="E560" s="3">
+        <v>73</v>
+      </c>
+      <c r="F560" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="561" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A561" s="2">
+        <v>7052</v>
+      </c>
+      <c r="B561" s="3">
+        <v>9</v>
+      </c>
+      <c r="C561" s="3">
+        <v>55</v>
+      </c>
+      <c r="D561" s="3">
+        <v>63</v>
+      </c>
+      <c r="E561" s="3">
+        <v>65</v>
+      </c>
+      <c r="F561" s="3">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11797,6 +11830,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11808,14 +11850,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11835,6 +11869,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFA79B4-22AF-4CAE-ACED-91AB0E9DD58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAA9FCB-55E0-4B7E-9A47-DE796D1A7288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57660" yWindow="75" windowWidth="14910" windowHeight="14565" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="19770" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F561"/>
+  <dimension ref="A1:F568"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -11618,43 +11618,183 @@
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A560" s="2">
+      <c r="A560">
         <v>7051</v>
       </c>
-      <c r="B560" s="3">
+      <c r="B560">
         <v>19</v>
       </c>
-      <c r="C560" s="3">
+      <c r="C560">
         <v>32</v>
       </c>
-      <c r="D560" s="3">
+      <c r="D560">
         <v>50</v>
       </c>
-      <c r="E560" s="3">
+      <c r="E560">
         <v>73</v>
       </c>
-      <c r="F560" s="3">
+      <c r="F560">
         <v>75</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A561" s="2">
+      <c r="A561">
         <v>7052</v>
       </c>
-      <c r="B561" s="3">
+      <c r="B561">
         <v>9</v>
       </c>
-      <c r="C561" s="3">
+      <c r="C561">
         <v>55</v>
       </c>
-      <c r="D561" s="3">
+      <c r="D561">
         <v>63</v>
       </c>
-      <c r="E561" s="3">
+      <c r="E561">
         <v>65</v>
       </c>
-      <c r="F561" s="3">
+      <c r="F561">
         <v>80</v>
+      </c>
+    </row>
+    <row r="562" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A562" s="2">
+        <v>7053</v>
+      </c>
+      <c r="B562" s="3">
+        <v>2</v>
+      </c>
+      <c r="C562" s="3">
+        <v>15</v>
+      </c>
+      <c r="D562" s="3">
+        <v>54</v>
+      </c>
+      <c r="E562" s="3">
+        <v>63</v>
+      </c>
+      <c r="F562" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="563" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A563" s="2">
+        <v>7054</v>
+      </c>
+      <c r="B563" s="3">
+        <v>2</v>
+      </c>
+      <c r="C563" s="3">
+        <v>11</v>
+      </c>
+      <c r="D563" s="3">
+        <v>34</v>
+      </c>
+      <c r="E563" s="3">
+        <v>63</v>
+      </c>
+      <c r="F563" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="564" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A564" s="2">
+        <v>7055</v>
+      </c>
+      <c r="B564" s="3">
+        <v>7</v>
+      </c>
+      <c r="C564" s="3">
+        <v>20</v>
+      </c>
+      <c r="D564" s="3">
+        <v>22</v>
+      </c>
+      <c r="E564" s="3">
+        <v>38</v>
+      </c>
+      <c r="F564" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="565" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A565" s="2">
+        <v>7056</v>
+      </c>
+      <c r="B565" s="3">
+        <v>28</v>
+      </c>
+      <c r="C565" s="3">
+        <v>41</v>
+      </c>
+      <c r="D565" s="3">
+        <v>43</v>
+      </c>
+      <c r="E565" s="3">
+        <v>50</v>
+      </c>
+      <c r="F565" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="566" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A566" s="2">
+        <v>7057</v>
+      </c>
+      <c r="B566" s="3">
+        <v>34</v>
+      </c>
+      <c r="C566" s="3">
+        <v>38</v>
+      </c>
+      <c r="D566" s="3">
+        <v>47</v>
+      </c>
+      <c r="E566" s="3">
+        <v>63</v>
+      </c>
+      <c r="F566" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="567" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A567" s="2">
+        <v>7058</v>
+      </c>
+      <c r="B567" s="3">
+        <v>8</v>
+      </c>
+      <c r="C567" s="3">
+        <v>26</v>
+      </c>
+      <c r="D567" s="3">
+        <v>27</v>
+      </c>
+      <c r="E567" s="3">
+        <v>66</v>
+      </c>
+      <c r="F567" s="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="568" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A568" s="2">
+        <v>7059</v>
+      </c>
+      <c r="B568" s="3">
+        <v>27</v>
+      </c>
+      <c r="C568" s="3">
+        <v>47</v>
+      </c>
+      <c r="D568" s="3">
+        <v>57</v>
+      </c>
+      <c r="E568" s="3">
+        <v>70</v>
+      </c>
+      <c r="F568" s="3">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -11663,6 +11803,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11830,15 +11979,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11850,6 +11990,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11869,14 +12017,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAA9FCB-55E0-4B7E-9A47-DE796D1A7288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09561909-D2AD-4091-AC06-1FEF38346935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="19770" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="61245" yWindow="870" windowWidth="21360" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F568"/>
+  <dimension ref="A1:F571"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -11658,143 +11658,203 @@
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A562" s="2">
+      <c r="A562">
         <v>7053</v>
       </c>
-      <c r="B562" s="3">
+      <c r="B562">
         <v>2</v>
       </c>
-      <c r="C562" s="3">
+      <c r="C562">
         <v>15</v>
       </c>
-      <c r="D562" s="3">
+      <c r="D562">
         <v>54</v>
       </c>
-      <c r="E562" s="3">
+      <c r="E562">
         <v>63</v>
       </c>
-      <c r="F562" s="3">
+      <c r="F562">
         <v>72</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A563" s="2">
+      <c r="A563">
         <v>7054</v>
       </c>
-      <c r="B563" s="3">
+      <c r="B563">
         <v>2</v>
       </c>
-      <c r="C563" s="3">
+      <c r="C563">
         <v>11</v>
       </c>
-      <c r="D563" s="3">
+      <c r="D563">
         <v>34</v>
       </c>
-      <c r="E563" s="3">
+      <c r="E563">
         <v>63</v>
       </c>
-      <c r="F563" s="3">
+      <c r="F563">
         <v>68</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A564" s="2">
+      <c r="A564">
         <v>7055</v>
       </c>
-      <c r="B564" s="3">
+      <c r="B564">
         <v>7</v>
       </c>
-      <c r="C564" s="3">
+      <c r="C564">
         <v>20</v>
       </c>
-      <c r="D564" s="3">
+      <c r="D564">
         <v>22</v>
       </c>
-      <c r="E564" s="3">
+      <c r="E564">
         <v>38</v>
       </c>
-      <c r="F564" s="3">
+      <c r="F564">
         <v>66</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A565" s="2">
+      <c r="A565">
         <v>7056</v>
       </c>
-      <c r="B565" s="3">
+      <c r="B565">
         <v>28</v>
       </c>
-      <c r="C565" s="3">
+      <c r="C565">
         <v>41</v>
       </c>
-      <c r="D565" s="3">
+      <c r="D565">
         <v>43</v>
       </c>
-      <c r="E565" s="3">
+      <c r="E565">
         <v>50</v>
       </c>
-      <c r="F565" s="3">
+      <c r="F565">
         <v>57</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A566" s="2">
+      <c r="A566">
         <v>7057</v>
       </c>
-      <c r="B566" s="3">
+      <c r="B566">
         <v>34</v>
       </c>
-      <c r="C566" s="3">
+      <c r="C566">
         <v>38</v>
       </c>
-      <c r="D566" s="3">
+      <c r="D566">
         <v>47</v>
       </c>
-      <c r="E566" s="3">
+      <c r="E566">
         <v>63</v>
       </c>
-      <c r="F566" s="3">
+      <c r="F566">
         <v>75</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A567" s="2">
+      <c r="A567">
         <v>7058</v>
       </c>
-      <c r="B567" s="3">
+      <c r="B567">
         <v>8</v>
       </c>
-      <c r="C567" s="3">
+      <c r="C567">
         <v>26</v>
       </c>
-      <c r="D567" s="3">
+      <c r="D567">
         <v>27</v>
       </c>
-      <c r="E567" s="3">
+      <c r="E567">
         <v>66</v>
       </c>
-      <c r="F567" s="3">
+      <c r="F567">
         <v>79</v>
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A568" s="2">
+      <c r="A568">
         <v>7059</v>
       </c>
-      <c r="B568" s="3">
+      <c r="B568">
         <v>27</v>
       </c>
-      <c r="C568" s="3">
+      <c r="C568">
         <v>47</v>
       </c>
-      <c r="D568" s="3">
+      <c r="D568">
         <v>57</v>
       </c>
-      <c r="E568" s="3">
+      <c r="E568">
         <v>70</v>
       </c>
-      <c r="F568" s="3">
+      <c r="F568">
         <v>78</v>
+      </c>
+    </row>
+    <row r="569" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A569" s="2">
+        <v>7060</v>
+      </c>
+      <c r="B569" s="3">
+        <v>2</v>
+      </c>
+      <c r="C569" s="3">
+        <v>19</v>
+      </c>
+      <c r="D569" s="3">
+        <v>27</v>
+      </c>
+      <c r="E569" s="3">
+        <v>38</v>
+      </c>
+      <c r="F569" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="570" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A570" s="2">
+        <v>7061</v>
+      </c>
+      <c r="B570" s="3">
+        <v>19</v>
+      </c>
+      <c r="C570" s="3">
+        <v>49</v>
+      </c>
+      <c r="D570" s="3">
+        <v>59</v>
+      </c>
+      <c r="E570" s="3">
+        <v>60</v>
+      </c>
+      <c r="F570" s="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="571" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A571" s="2">
+        <v>7062</v>
+      </c>
+      <c r="B571" s="3">
+        <v>15</v>
+      </c>
+      <c r="C571" s="3">
+        <v>19</v>
+      </c>
+      <c r="D571" s="3">
+        <v>42</v>
+      </c>
+      <c r="E571" s="3">
+        <v>50</v>
+      </c>
+      <c r="F571" s="3">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -11803,15 +11863,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11979,6 +12030,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11990,14 +12050,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12017,6 +12069,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09561909-D2AD-4091-AC06-1FEF38346935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE133A83-F18D-453E-81CB-C723949F634D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61245" yWindow="870" windowWidth="21360" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58110" yWindow="7665" windowWidth="26985" windowHeight="7695" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F571"/>
+  <dimension ref="A1:F575"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -11798,63 +11798,143 @@
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A569" s="2">
+      <c r="A569">
         <v>7060</v>
       </c>
-      <c r="B569" s="3">
+      <c r="B569">
         <v>2</v>
       </c>
-      <c r="C569" s="3">
+      <c r="C569">
         <v>19</v>
       </c>
-      <c r="D569" s="3">
+      <c r="D569">
         <v>27</v>
       </c>
-      <c r="E569" s="3">
+      <c r="E569">
         <v>38</v>
       </c>
-      <c r="F569" s="3">
+      <c r="F569">
         <v>69</v>
       </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A570" s="2">
+      <c r="A570">
         <v>7061</v>
       </c>
-      <c r="B570" s="3">
+      <c r="B570">
         <v>19</v>
       </c>
-      <c r="C570" s="3">
+      <c r="C570">
         <v>49</v>
       </c>
-      <c r="D570" s="3">
+      <c r="D570">
         <v>59</v>
       </c>
-      <c r="E570" s="3">
+      <c r="E570">
         <v>60</v>
       </c>
-      <c r="F570" s="3">
+      <c r="F570">
         <v>71</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A571" s="2">
+      <c r="A571">
         <v>7062</v>
       </c>
-      <c r="B571" s="3">
+      <c r="B571">
         <v>15</v>
       </c>
-      <c r="C571" s="3">
+      <c r="C571">
         <v>19</v>
       </c>
-      <c r="D571" s="3">
+      <c r="D571">
         <v>42</v>
       </c>
-      <c r="E571" s="3">
+      <c r="E571">
         <v>50</v>
       </c>
-      <c r="F571" s="3">
+      <c r="F571">
         <v>63</v>
+      </c>
+    </row>
+    <row r="572" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A572" s="2">
+        <v>7063</v>
+      </c>
+      <c r="B572" s="3">
+        <v>9</v>
+      </c>
+      <c r="C572" s="3">
+        <v>36</v>
+      </c>
+      <c r="D572" s="3">
+        <v>55</v>
+      </c>
+      <c r="E572" s="3">
+        <v>61</v>
+      </c>
+      <c r="F572" s="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="573" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A573" s="2">
+        <v>7064</v>
+      </c>
+      <c r="B573" s="3">
+        <v>15</v>
+      </c>
+      <c r="C573" s="3">
+        <v>24</v>
+      </c>
+      <c r="D573" s="3">
+        <v>29</v>
+      </c>
+      <c r="E573" s="3">
+        <v>53</v>
+      </c>
+      <c r="F573" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="574" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A574" s="2">
+        <v>7065</v>
+      </c>
+      <c r="B574" s="3">
+        <v>16</v>
+      </c>
+      <c r="C574" s="3">
+        <v>18</v>
+      </c>
+      <c r="D574" s="3">
+        <v>20</v>
+      </c>
+      <c r="E574" s="3">
+        <v>40</v>
+      </c>
+      <c r="F574" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="575" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A575" s="2">
+        <v>7066</v>
+      </c>
+      <c r="B575" s="3">
+        <v>12</v>
+      </c>
+      <c r="C575" s="3">
+        <v>14</v>
+      </c>
+      <c r="D575" s="3">
+        <v>30</v>
+      </c>
+      <c r="E575" s="3">
+        <v>47</v>
+      </c>
+      <c r="F575" s="3">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -11863,6 +11943,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12030,15 +12119,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12050,6 +12130,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12069,14 +12157,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE133A83-F18D-453E-81CB-C723949F634D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CE992F-3E25-4636-993C-04EAC3EB6987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58110" yWindow="7665" windowWidth="26985" windowHeight="7695" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="23662" windowHeight="10170" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F575"/>
+  <dimension ref="A1:F586"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -11858,83 +11858,303 @@
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A572" s="2">
+      <c r="A572">
         <v>7063</v>
       </c>
-      <c r="B572" s="3">
+      <c r="B572">
         <v>9</v>
       </c>
-      <c r="C572" s="3">
+      <c r="C572">
         <v>36</v>
       </c>
-      <c r="D572" s="3">
+      <c r="D572">
         <v>55</v>
       </c>
-      <c r="E572" s="3">
+      <c r="E572">
         <v>61</v>
       </c>
-      <c r="F572" s="3">
+      <c r="F572">
         <v>79</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A573" s="2">
+      <c r="A573">
         <v>7064</v>
       </c>
-      <c r="B573" s="3">
+      <c r="B573">
         <v>15</v>
       </c>
-      <c r="C573" s="3">
+      <c r="C573">
         <v>24</v>
       </c>
-      <c r="D573" s="3">
+      <c r="D573">
         <v>29</v>
       </c>
-      <c r="E573" s="3">
+      <c r="E573">
         <v>53</v>
       </c>
-      <c r="F573" s="3">
+      <c r="F573">
         <v>60</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A574" s="2">
+      <c r="A574">
         <v>7065</v>
       </c>
-      <c r="B574" s="3">
+      <c r="B574">
         <v>16</v>
       </c>
-      <c r="C574" s="3">
+      <c r="C574">
         <v>18</v>
       </c>
-      <c r="D574" s="3">
+      <c r="D574">
         <v>20</v>
       </c>
-      <c r="E574" s="3">
+      <c r="E574">
         <v>40</v>
       </c>
-      <c r="F574" s="3">
+      <c r="F574">
         <v>56</v>
       </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A575" s="2">
+      <c r="A575">
         <v>7066</v>
       </c>
-      <c r="B575" s="3">
+      <c r="B575">
         <v>12</v>
       </c>
-      <c r="C575" s="3">
+      <c r="C575">
         <v>14</v>
       </c>
-      <c r="D575" s="3">
+      <c r="D575">
         <v>30</v>
       </c>
-      <c r="E575" s="3">
+      <c r="E575">
         <v>47</v>
       </c>
-      <c r="F575" s="3">
+      <c r="F575">
         <v>76</v>
+      </c>
+    </row>
+    <row r="576" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A576" s="2">
+        <v>7067</v>
+      </c>
+      <c r="B576" s="3">
+        <v>5</v>
+      </c>
+      <c r="C576" s="3">
+        <v>8</v>
+      </c>
+      <c r="D576" s="3">
+        <v>18</v>
+      </c>
+      <c r="E576" s="3">
+        <v>25</v>
+      </c>
+      <c r="F576" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="577" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A577" s="2">
+        <v>7068</v>
+      </c>
+      <c r="B577" s="3">
+        <v>6</v>
+      </c>
+      <c r="C577" s="3">
+        <v>16</v>
+      </c>
+      <c r="D577" s="3">
+        <v>39</v>
+      </c>
+      <c r="E577" s="3">
+        <v>69</v>
+      </c>
+      <c r="F577" s="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="578" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A578" s="2">
+        <v>7069</v>
+      </c>
+      <c r="B578" s="3">
+        <v>13</v>
+      </c>
+      <c r="C578" s="3">
+        <v>20</v>
+      </c>
+      <c r="D578" s="3">
+        <v>33</v>
+      </c>
+      <c r="E578" s="3">
+        <v>56</v>
+      </c>
+      <c r="F578" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="579" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A579" s="2">
+        <v>7070</v>
+      </c>
+      <c r="B579" s="3">
+        <v>15</v>
+      </c>
+      <c r="C579" s="3">
+        <v>31</v>
+      </c>
+      <c r="D579" s="3">
+        <v>36</v>
+      </c>
+      <c r="E579" s="3">
+        <v>64</v>
+      </c>
+      <c r="F579" s="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="580" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A580" s="2">
+        <v>7071</v>
+      </c>
+      <c r="B580" s="3">
+        <v>6</v>
+      </c>
+      <c r="C580" s="3">
+        <v>14</v>
+      </c>
+      <c r="D580" s="3">
+        <v>34</v>
+      </c>
+      <c r="E580" s="3">
+        <v>38</v>
+      </c>
+      <c r="F580" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="581" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A581" s="2">
+        <v>7072</v>
+      </c>
+      <c r="B581" s="3">
+        <v>3</v>
+      </c>
+      <c r="C581" s="3">
+        <v>13</v>
+      </c>
+      <c r="D581" s="3">
+        <v>25</v>
+      </c>
+      <c r="E581" s="3">
+        <v>56</v>
+      </c>
+      <c r="F581" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="582" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A582" s="2">
+        <v>7073</v>
+      </c>
+      <c r="B582" s="3">
+        <v>4</v>
+      </c>
+      <c r="C582" s="3">
+        <v>9</v>
+      </c>
+      <c r="D582" s="3">
+        <v>32</v>
+      </c>
+      <c r="E582" s="3">
+        <v>34</v>
+      </c>
+      <c r="F582" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="583" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A583" s="2">
+        <v>7074</v>
+      </c>
+      <c r="B583" s="3">
+        <v>17</v>
+      </c>
+      <c r="C583" s="3">
+        <v>28</v>
+      </c>
+      <c r="D583" s="3">
+        <v>29</v>
+      </c>
+      <c r="E583" s="3">
+        <v>41</v>
+      </c>
+      <c r="F583" s="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="584" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A584" s="2">
+        <v>7075</v>
+      </c>
+      <c r="B584" s="3">
+        <v>2</v>
+      </c>
+      <c r="C584" s="3">
+        <v>4</v>
+      </c>
+      <c r="D584" s="3">
+        <v>20</v>
+      </c>
+      <c r="E584" s="3">
+        <v>50</v>
+      </c>
+      <c r="F584" s="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="585" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A585" s="2">
+        <v>7076</v>
+      </c>
+      <c r="B585" s="3">
+        <v>1</v>
+      </c>
+      <c r="C585" s="3">
+        <v>18</v>
+      </c>
+      <c r="D585" s="3">
+        <v>22</v>
+      </c>
+      <c r="E585" s="3">
+        <v>35</v>
+      </c>
+      <c r="F585" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="586" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A586" s="2">
+        <v>7077</v>
+      </c>
+      <c r="B586" s="3">
+        <v>2</v>
+      </c>
+      <c r="C586" s="3">
+        <v>3</v>
+      </c>
+      <c r="D586" s="3">
+        <v>30</v>
+      </c>
+      <c r="E586" s="3">
+        <v>46</v>
+      </c>
+      <c r="F586" s="3">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -11943,15 +12163,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12119,6 +12330,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12130,14 +12350,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12157,6 +12369,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CE992F-3E25-4636-993C-04EAC3EB6987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80CBA936-266E-4FBF-A374-DB61EDAD7F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="23662" windowHeight="10170" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="405" yWindow="248" windowWidth="25680" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -103,13 +103,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F586"/>
+  <dimension ref="A1:F587"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -11938,223 +11936,243 @@
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A576" s="2">
+      <c r="A576">
         <v>7067</v>
       </c>
-      <c r="B576" s="3">
+      <c r="B576">
         <v>5</v>
       </c>
-      <c r="C576" s="3">
+      <c r="C576">
         <v>8</v>
       </c>
-      <c r="D576" s="3">
+      <c r="D576">
         <v>18</v>
       </c>
-      <c r="E576" s="3">
+      <c r="E576">
         <v>25</v>
       </c>
-      <c r="F576" s="3">
+      <c r="F576">
         <v>55</v>
       </c>
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A577" s="2">
+      <c r="A577">
         <v>7068</v>
       </c>
-      <c r="B577" s="3">
+      <c r="B577">
         <v>6</v>
       </c>
-      <c r="C577" s="3">
+      <c r="C577">
         <v>16</v>
       </c>
-      <c r="D577" s="3">
+      <c r="D577">
         <v>39</v>
       </c>
-      <c r="E577" s="3">
+      <c r="E577">
         <v>69</v>
       </c>
-      <c r="F577" s="3">
+      <c r="F577">
         <v>74</v>
       </c>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A578" s="2">
+      <c r="A578">
         <v>7069</v>
       </c>
-      <c r="B578" s="3">
+      <c r="B578">
         <v>13</v>
       </c>
-      <c r="C578" s="3">
+      <c r="C578">
         <v>20</v>
       </c>
-      <c r="D578" s="3">
+      <c r="D578">
         <v>33</v>
       </c>
-      <c r="E578" s="3">
+      <c r="E578">
         <v>56</v>
       </c>
-      <c r="F578" s="3">
+      <c r="F578">
         <v>65</v>
       </c>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A579" s="2">
+      <c r="A579">
         <v>7070</v>
       </c>
-      <c r="B579" s="3">
+      <c r="B579">
         <v>15</v>
       </c>
-      <c r="C579" s="3">
+      <c r="C579">
         <v>31</v>
       </c>
-      <c r="D579" s="3">
+      <c r="D579">
         <v>36</v>
       </c>
-      <c r="E579" s="3">
+      <c r="E579">
         <v>64</v>
       </c>
-      <c r="F579" s="3">
+      <c r="F579">
         <v>74</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A580" s="2">
+      <c r="A580">
         <v>7071</v>
       </c>
-      <c r="B580" s="3">
+      <c r="B580">
         <v>6</v>
       </c>
-      <c r="C580" s="3">
+      <c r="C580">
         <v>14</v>
       </c>
-      <c r="D580" s="3">
+      <c r="D580">
         <v>34</v>
       </c>
-      <c r="E580" s="3">
+      <c r="E580">
         <v>38</v>
       </c>
-      <c r="F580" s="3">
+      <c r="F580">
         <v>56</v>
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A581" s="2">
+      <c r="A581">
         <v>7072</v>
       </c>
-      <c r="B581" s="3">
+      <c r="B581">
         <v>3</v>
       </c>
-      <c r="C581" s="3">
+      <c r="C581">
         <v>13</v>
       </c>
-      <c r="D581" s="3">
+      <c r="D581">
         <v>25</v>
       </c>
-      <c r="E581" s="3">
+      <c r="E581">
         <v>56</v>
       </c>
-      <c r="F581" s="3">
+      <c r="F581">
         <v>65</v>
       </c>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A582" s="2">
+      <c r="A582">
         <v>7073</v>
       </c>
-      <c r="B582" s="3">
+      <c r="B582">
         <v>4</v>
       </c>
-      <c r="C582" s="3">
+      <c r="C582">
         <v>9</v>
       </c>
-      <c r="D582" s="3">
+      <c r="D582">
         <v>32</v>
       </c>
-      <c r="E582" s="3">
+      <c r="E582">
         <v>34</v>
       </c>
-      <c r="F582" s="3">
+      <c r="F582">
         <v>46</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A583" s="2">
+      <c r="A583">
         <v>7074</v>
       </c>
-      <c r="B583" s="3">
+      <c r="B583">
         <v>17</v>
       </c>
-      <c r="C583" s="3">
+      <c r="C583">
         <v>28</v>
       </c>
-      <c r="D583" s="3">
+      <c r="D583">
         <v>29</v>
       </c>
-      <c r="E583" s="3">
+      <c r="E583">
         <v>41</v>
       </c>
-      <c r="F583" s="3">
+      <c r="F583">
         <v>77</v>
       </c>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A584" s="2">
+      <c r="A584">
         <v>7075</v>
       </c>
-      <c r="B584" s="3">
+      <c r="B584">
         <v>2</v>
       </c>
-      <c r="C584" s="3">
+      <c r="C584">
         <v>4</v>
       </c>
-      <c r="D584" s="3">
+      <c r="D584">
         <v>20</v>
       </c>
-      <c r="E584" s="3">
+      <c r="E584">
         <v>50</v>
       </c>
-      <c r="F584" s="3">
+      <c r="F584">
         <v>73</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A585" s="2">
+      <c r="A585">
         <v>7076</v>
       </c>
-      <c r="B585" s="3">
+      <c r="B585">
         <v>1</v>
       </c>
-      <c r="C585" s="3">
+      <c r="C585">
         <v>18</v>
       </c>
-      <c r="D585" s="3">
+      <c r="D585">
         <v>22</v>
       </c>
-      <c r="E585" s="3">
+      <c r="E585">
         <v>35</v>
       </c>
-      <c r="F585" s="3">
+      <c r="F585">
         <v>41</v>
       </c>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A586" s="2">
+      <c r="A586">
         <v>7077</v>
       </c>
-      <c r="B586" s="3">
+      <c r="B586">
         <v>2</v>
       </c>
-      <c r="C586" s="3">
+      <c r="C586">
         <v>3</v>
       </c>
-      <c r="D586" s="3">
+      <c r="D586">
         <v>30</v>
       </c>
-      <c r="E586" s="3">
+      <c r="E586">
         <v>46</v>
       </c>
-      <c r="F586" s="3">
+      <c r="F586">
         <v>77</v>
+      </c>
+    </row>
+    <row r="587" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A587">
+        <v>7078</v>
+      </c>
+      <c r="B587">
+        <v>16</v>
+      </c>
+      <c r="C587">
+        <v>31</v>
+      </c>
+      <c r="D587">
+        <v>55</v>
+      </c>
+      <c r="E587">
+        <v>66</v>
+      </c>
+      <c r="F587">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -12163,6 +12181,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12330,15 +12357,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12350,6 +12368,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12369,14 +12395,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80CBA936-266E-4FBF-A374-DB61EDAD7F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8903677-37EA-4162-9AC0-99EA7D9EA36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="248" windowWidth="25680" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58365" yWindow="1125" windowWidth="25680" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F587"/>
+  <dimension ref="A1:F588"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -12175,21 +12175,32 @@
         <v>71</v>
       </c>
     </row>
+    <row r="588" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A588">
+        <v>7079</v>
+      </c>
+      <c r="B588">
+        <v>3</v>
+      </c>
+      <c r="C588">
+        <v>29</v>
+      </c>
+      <c r="D588">
+        <v>46</v>
+      </c>
+      <c r="E588">
+        <v>50</v>
+      </c>
+      <c r="F588">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12357,6 +12368,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12368,14 +12388,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12395,6 +12407,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8903677-37EA-4162-9AC0-99EA7D9EA36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F32CE2-8C3E-4A25-94F8-D46DBEDABE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58365" yWindow="1125" windowWidth="25680" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58140" yWindow="780" windowWidth="13560" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F588"/>
+  <dimension ref="A1:F590"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -12195,12 +12195,61 @@
         <v>55</v>
       </c>
     </row>
+    <row r="589" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A589">
+        <v>7080</v>
+      </c>
+      <c r="B589">
+        <v>2</v>
+      </c>
+      <c r="C589">
+        <v>19</v>
+      </c>
+      <c r="D589">
+        <v>24</v>
+      </c>
+      <c r="E589">
+        <v>39</v>
+      </c>
+      <c r="F589">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="590" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A590">
+        <v>7081</v>
+      </c>
+      <c r="B590">
+        <v>14</v>
+      </c>
+      <c r="C590">
+        <v>22</v>
+      </c>
+      <c r="D590">
+        <v>28</v>
+      </c>
+      <c r="E590">
+        <v>40</v>
+      </c>
+      <c r="F590">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12368,15 +12417,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12388,6 +12428,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12407,14 +12455,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F32CE2-8C3E-4A25-94F8-D46DBEDABE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02253A4B-EB05-43AF-A6AC-735DE10DE4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58140" yWindow="780" windowWidth="13560" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="2318" yWindow="525" windowWidth="25545" windowHeight="10118" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F590"/>
+  <dimension ref="A1:F592"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -12235,21 +12235,52 @@
         <v>45</v>
       </c>
     </row>
+    <row r="591" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A591">
+        <v>7082</v>
+      </c>
+      <c r="B591">
+        <v>17</v>
+      </c>
+      <c r="C591">
+        <v>38</v>
+      </c>
+      <c r="D591">
+        <v>50</v>
+      </c>
+      <c r="E591">
+        <v>63</v>
+      </c>
+      <c r="F591">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="592" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A592">
+        <v>7083</v>
+      </c>
+      <c r="B592">
+        <v>15</v>
+      </c>
+      <c r="C592">
+        <v>26</v>
+      </c>
+      <c r="D592">
+        <v>45</v>
+      </c>
+      <c r="E592">
+        <v>73</v>
+      </c>
+      <c r="F592">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12417,6 +12448,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12428,14 +12468,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12455,6 +12487,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02253A4B-EB05-43AF-A6AC-735DE10DE4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109D4284-A3BE-4935-A6F6-2E898CBD4EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2318" yWindow="525" windowWidth="25545" windowHeight="10118" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="0" yWindow="1132" windowWidth="25545" windowHeight="10118" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F592"/>
+  <dimension ref="A1:F594"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -12275,12 +12275,61 @@
         <v>77</v>
       </c>
     </row>
+    <row r="593" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A593">
+        <v>7084</v>
+      </c>
+      <c r="B593">
+        <v>17</v>
+      </c>
+      <c r="C593">
+        <v>22</v>
+      </c>
+      <c r="D593">
+        <v>36</v>
+      </c>
+      <c r="E593">
+        <v>54</v>
+      </c>
+      <c r="F593">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="594" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A594">
+        <v>7085</v>
+      </c>
+      <c r="B594">
+        <v>8</v>
+      </c>
+      <c r="C594">
+        <v>14</v>
+      </c>
+      <c r="D594">
+        <v>49</v>
+      </c>
+      <c r="E594">
+        <v>58</v>
+      </c>
+      <c r="F594">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12448,15 +12497,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12468,6 +12508,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12487,14 +12535,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109D4284-A3BE-4935-A6F6-2E898CBD4EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A17C7B-870C-480B-A68A-DFCB4366FD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1132" windowWidth="25545" windowHeight="10118" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="3825" yWindow="240" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -103,11 +103,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F594"/>
+  <dimension ref="A1:F602"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -12315,21 +12317,172 @@
         <v>78</v>
       </c>
     </row>
+    <row r="595" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A595" s="2">
+        <v>7086</v>
+      </c>
+      <c r="B595" s="3">
+        <v>1</v>
+      </c>
+      <c r="C595" s="3">
+        <v>22</v>
+      </c>
+      <c r="D595" s="3">
+        <v>39</v>
+      </c>
+      <c r="E595" s="3">
+        <v>58</v>
+      </c>
+      <c r="F595" s="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="596" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A596" s="2">
+        <v>7087</v>
+      </c>
+      <c r="B596" s="3">
+        <v>25</v>
+      </c>
+      <c r="C596" s="3">
+        <v>27</v>
+      </c>
+      <c r="D596" s="3">
+        <v>51</v>
+      </c>
+      <c r="E596" s="3">
+        <v>58</v>
+      </c>
+      <c r="F596" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="597" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A597" s="2">
+        <v>7088</v>
+      </c>
+      <c r="B597" s="3">
+        <v>16</v>
+      </c>
+      <c r="C597" s="3">
+        <v>26</v>
+      </c>
+      <c r="D597" s="3">
+        <v>41</v>
+      </c>
+      <c r="E597" s="3">
+        <v>42</v>
+      </c>
+      <c r="F597" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="598" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A598" s="2">
+        <v>7089</v>
+      </c>
+      <c r="B598" s="3">
+        <v>26</v>
+      </c>
+      <c r="C598" s="3">
+        <v>33</v>
+      </c>
+      <c r="D598" s="3">
+        <v>40</v>
+      </c>
+      <c r="E598" s="3">
+        <v>55</v>
+      </c>
+      <c r="F598" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="599" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A599" s="2">
+        <v>7090</v>
+      </c>
+      <c r="B599" s="3">
+        <v>5</v>
+      </c>
+      <c r="C599" s="3">
+        <v>46</v>
+      </c>
+      <c r="D599" s="3">
+        <v>62</v>
+      </c>
+      <c r="E599" s="3">
+        <v>72</v>
+      </c>
+      <c r="F599" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="600" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A600" s="2">
+        <v>7091</v>
+      </c>
+      <c r="B600" s="3">
+        <v>5</v>
+      </c>
+      <c r="C600" s="3">
+        <v>42</v>
+      </c>
+      <c r="D600" s="3">
+        <v>53</v>
+      </c>
+      <c r="E600" s="3">
+        <v>57</v>
+      </c>
+      <c r="F600" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="601" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A601" s="2">
+        <v>7092</v>
+      </c>
+      <c r="B601" s="3">
+        <v>23</v>
+      </c>
+      <c r="C601" s="3">
+        <v>30</v>
+      </c>
+      <c r="D601" s="3">
+        <v>47</v>
+      </c>
+      <c r="E601" s="3">
+        <v>70</v>
+      </c>
+      <c r="F601" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="602" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A602" s="2">
+        <v>7093</v>
+      </c>
+      <c r="B602" s="3">
+        <v>21</v>
+      </c>
+      <c r="C602" s="3">
+        <v>41</v>
+      </c>
+      <c r="D602" s="3">
+        <v>57</v>
+      </c>
+      <c r="E602" s="3">
+        <v>63</v>
+      </c>
+      <c r="F602" s="3">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12497,6 +12650,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12508,14 +12670,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12535,6 +12689,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A17C7B-870C-480B-A68A-DFCB4366FD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BF8E6A-087B-4F49-B311-D6BD56B3E048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3825" yWindow="240" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="5423" yWindow="1530" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -103,13 +103,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F602"/>
+  <dimension ref="A1:F603"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -12318,163 +12316,183 @@
       </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A595" s="2">
+      <c r="A595">
         <v>7086</v>
       </c>
-      <c r="B595" s="3">
+      <c r="B595">
         <v>1</v>
       </c>
-      <c r="C595" s="3">
+      <c r="C595">
         <v>22</v>
       </c>
-      <c r="D595" s="3">
+      <c r="D595">
         <v>39</v>
       </c>
-      <c r="E595" s="3">
+      <c r="E595">
         <v>58</v>
       </c>
-      <c r="F595" s="3">
+      <c r="F595">
         <v>61</v>
       </c>
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A596" s="2">
+      <c r="A596">
         <v>7087</v>
       </c>
-      <c r="B596" s="3">
+      <c r="B596">
         <v>25</v>
       </c>
-      <c r="C596" s="3">
+      <c r="C596">
         <v>27</v>
       </c>
-      <c r="D596" s="3">
+      <c r="D596">
         <v>51</v>
       </c>
-      <c r="E596" s="3">
+      <c r="E596">
         <v>58</v>
       </c>
-      <c r="F596" s="3">
+      <c r="F596">
         <v>65</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A597" s="2">
+      <c r="A597">
         <v>7088</v>
       </c>
-      <c r="B597" s="3">
+      <c r="B597">
         <v>16</v>
       </c>
-      <c r="C597" s="3">
+      <c r="C597">
         <v>26</v>
       </c>
-      <c r="D597" s="3">
+      <c r="D597">
         <v>41</v>
       </c>
-      <c r="E597" s="3">
+      <c r="E597">
         <v>42</v>
       </c>
-      <c r="F597" s="3">
+      <c r="F597">
         <v>67</v>
       </c>
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A598" s="2">
+      <c r="A598">
         <v>7089</v>
       </c>
-      <c r="B598" s="3">
+      <c r="B598">
         <v>26</v>
       </c>
-      <c r="C598" s="3">
+      <c r="C598">
         <v>33</v>
       </c>
-      <c r="D598" s="3">
+      <c r="D598">
         <v>40</v>
       </c>
-      <c r="E598" s="3">
+      <c r="E598">
         <v>55</v>
       </c>
-      <c r="F598" s="3">
+      <c r="F598">
         <v>69</v>
       </c>
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A599" s="2">
+      <c r="A599">
         <v>7090</v>
       </c>
-      <c r="B599" s="3">
+      <c r="B599">
         <v>5</v>
       </c>
-      <c r="C599" s="3">
+      <c r="C599">
         <v>46</v>
       </c>
-      <c r="D599" s="3">
+      <c r="D599">
         <v>62</v>
       </c>
-      <c r="E599" s="3">
+      <c r="E599">
         <v>72</v>
       </c>
-      <c r="F599" s="3">
+      <c r="F599">
         <v>78</v>
       </c>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A600" s="2">
+      <c r="A600">
         <v>7091</v>
       </c>
-      <c r="B600" s="3">
+      <c r="B600">
         <v>5</v>
       </c>
-      <c r="C600" s="3">
+      <c r="C600">
         <v>42</v>
       </c>
-      <c r="D600" s="3">
+      <c r="D600">
         <v>53</v>
       </c>
-      <c r="E600" s="3">
+      <c r="E600">
         <v>57</v>
       </c>
-      <c r="F600" s="3">
+      <c r="F600">
         <v>59</v>
       </c>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A601" s="2">
+      <c r="A601">
         <v>7092</v>
       </c>
-      <c r="B601" s="3">
+      <c r="B601">
         <v>23</v>
       </c>
-      <c r="C601" s="3">
+      <c r="C601">
         <v>30</v>
       </c>
-      <c r="D601" s="3">
+      <c r="D601">
         <v>47</v>
       </c>
-      <c r="E601" s="3">
+      <c r="E601">
         <v>70</v>
       </c>
-      <c r="F601" s="3">
+      <c r="F601">
         <v>80</v>
       </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A602" s="2">
+      <c r="A602">
         <v>7093</v>
       </c>
-      <c r="B602" s="3">
+      <c r="B602">
         <v>21</v>
       </c>
-      <c r="C602" s="3">
+      <c r="C602">
         <v>41</v>
       </c>
-      <c r="D602" s="3">
+      <c r="D602">
         <v>57</v>
       </c>
-      <c r="E602" s="3">
+      <c r="E602">
         <v>63</v>
       </c>
-      <c r="F602" s="3">
+      <c r="F602">
         <v>64</v>
+      </c>
+    </row>
+    <row r="603" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A603">
+        <v>7094</v>
+      </c>
+      <c r="B603">
+        <v>17</v>
+      </c>
+      <c r="C603">
+        <v>24</v>
+      </c>
+      <c r="D603">
+        <v>26</v>
+      </c>
+      <c r="E603">
+        <v>42</v>
+      </c>
+      <c r="F603">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -12483,6 +12501,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12650,15 +12677,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12670,6 +12688,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12689,14 +12715,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BF8E6A-087B-4F49-B311-D6BD56B3E048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9994EBF-2749-4DAE-9D5E-875BE3A2C38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5423" yWindow="1530" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="4020" yWindow="1170" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -103,11 +103,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F603"/>
+  <dimension ref="A1:F605"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -12495,21 +12497,52 @@
         <v>80</v>
       </c>
     </row>
+    <row r="604" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A604" s="2">
+        <v>7095</v>
+      </c>
+      <c r="B604" s="3">
+        <v>6</v>
+      </c>
+      <c r="C604" s="3">
+        <v>17</v>
+      </c>
+      <c r="D604" s="3">
+        <v>19</v>
+      </c>
+      <c r="E604" s="3">
+        <v>39</v>
+      </c>
+      <c r="F604" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="605" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A605" s="2">
+        <v>7096</v>
+      </c>
+      <c r="B605" s="3">
+        <v>10</v>
+      </c>
+      <c r="C605" s="3">
+        <v>29</v>
+      </c>
+      <c r="D605" s="3">
+        <v>43</v>
+      </c>
+      <c r="E605" s="3">
+        <v>47</v>
+      </c>
+      <c r="F605" s="3">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12677,6 +12710,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12688,14 +12730,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12715,6 +12749,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>
